--- a/Base_Orcamentos.xlsx
+++ b/Base_Orcamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Orcamento\CONTROLE DE ORÇAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D6BA5A6-62C4-4AB7-B9D0-513EC8F9C49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4D3E9F0-45BC-4DC1-89CA-418BB950F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E2A164-C72A-41E5-BBAA-91E5197319FE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{22D79288-D1DE-4D60-B3F6-B0EE066BDDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Orcamentos" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="621">
   <si>
     <t>Nº Orçamento</t>
   </si>
@@ -575,7 +575,7 @@
     <t>GUILHERME PEREIRA COELHO LTDA</t>
   </si>
   <si>
-    <t>LUIZ</t>
+    <t>LUIZ FREITAS</t>
   </si>
   <si>
     <t>ROT 35mm X 135mm X 1 C | 135 M  c/ 1000 ROT</t>
@@ -1184,6 +1184,9 @@
     <t>CASAGRANDE SUPERMERCADOS LTDA</t>
   </si>
   <si>
+    <t>LUIZ  FREITAS</t>
+  </si>
+  <si>
     <t>ROT 55mm X 90mm X 1 C | 93 M  c/ 1000 ROT</t>
   </si>
   <si>
@@ -1448,400 +1451,439 @@
     <t>ORC 26100903</t>
   </si>
   <si>
+    <t>ORC 26100904</t>
+  </si>
+  <si>
+    <t>ORC 26100905</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 150mm X 1 C | 157 M  c/ 1040 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 90mm X 50mm X 1 C | 40 M  c/ 800 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26101301</t>
+  </si>
+  <si>
+    <t>DOMART ALIMENTOS</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>ETIQ 50mm X 53mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 150mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ETIQ 80mm X 65mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ETIQ 85mm X 65mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ETIQ 60mm X 60mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>MIG SUPERMERCADOS – ATACADO E VAREJO</t>
+  </si>
+  <si>
+    <t>ROT 65mm X 65mm X 1 C | 68 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ORC 26101302</t>
+  </si>
+  <si>
+    <t>ETIQ 150mm X 200mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ORC 26101401</t>
+  </si>
+  <si>
+    <t>DOMART ALIMENTOS LTDA.</t>
+  </si>
+  <si>
+    <t>ETIQ 120mm X 200mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ETIQ 120mm X 170mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ORC 26101402</t>
+  </si>
+  <si>
+    <t>ROT 65mm X 89mm X 1 C | 92 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ROT 80mm X 82mm X 1 C | 85 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ROT 79,5mm X 90mm X 1 C | 93 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ROT 58mm X 85mm X 1 C | 88 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ORC 26101405</t>
+  </si>
+  <si>
+    <t>CATABY INDÚSTRIA E COMÉRCIO DE CARNES LTDA</t>
+  </si>
+  <si>
+    <t>ROT 165mm X 75mm X 1 C | 312 M  c/ 4000 ROT</t>
+  </si>
+  <si>
+    <t>ETIQ 30mm X 120mm X 1 C | 492 M  c/ 4000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26101410</t>
+  </si>
+  <si>
+    <t>SUPERMERCADOS DALBEN LTDA</t>
+  </si>
+  <si>
+    <t>ROT 85mm X 135mm X 1 C | 69 M  c/ 500 ROT</t>
+  </si>
+  <si>
+    <t>ROT 145mm X 120mm X 1 C | 61,5 M  c/ 500 ROT</t>
+  </si>
+  <si>
+    <t>ETIQ 50mm X 50mm X  C | 53 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26101411</t>
+  </si>
+  <si>
+    <t>POINT CLEAN IND E COM PROD DE LIMPEZA LTDA-ME</t>
+  </si>
+  <si>
+    <t>ROT 120mm X 100mm X 1 C | 103 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ETIQ 140mm X 120mm X 1 C | 123 M  c/ 1020 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 145mm X 125mm X 1 C | 128 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 110mm X 180mm X 1 C | 183 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26101501</t>
+  </si>
+  <si>
+    <t>CARLOS A H BORGES </t>
+  </si>
+  <si>
+    <t>ETIQ 70mm X 40mm X 1 C | 35 M  c/ 810 ETIQ</t>
+  </si>
+  <si>
+    <t>A.42 BOPP Branco Fosco</t>
+  </si>
+  <si>
+    <t>ORC 26101503</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO MUNHOZ  </t>
+  </si>
+  <si>
+    <t>ROT 80mm X 60mm X 1 C | 63 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ORC 26101505</t>
+  </si>
+  <si>
+    <t>PANIFICADORA BONJARDIM</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 40mm X 1 C | 43 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26101510</t>
+  </si>
+  <si>
+    <t>FERNANDO BARTOLOMEU</t>
+  </si>
+  <si>
+    <t>ORC 26101512</t>
+  </si>
+  <si>
+    <t>M MAXI RANCHO</t>
+  </si>
+  <si>
+    <t>ROT 60mm X 75mm X 1 C | 78 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ETIQ 60mm X 75mm X 1 C | 78 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26101601</t>
+  </si>
+  <si>
+    <t>SAGE BRASIL INTERIORES AUTO. IND. E COM. LTDA</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 75mm X 1 C | 131,1 M  c/ 1680 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 50mm X 42mm X 1 C | 90 M  c/ 2000 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 60mm X 15mm X 1 C | 58,68 M  c/ 3260 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 110mm X 180mm X 1 C | 90 M  c/ 490 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26101602</t>
+  </si>
+  <si>
+    <t>ROGÉRIO FRANCISCO DA SILVA</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 120mm X 1 C | 60 M  c/ 500 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 101mm X 54mm X 1 C | 9,5 M  c/ 170 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26101603</t>
+  </si>
+  <si>
+    <t>MIG ATACADO E VAREJO LTDA</t>
+  </si>
+  <si>
+    <t>ROT 50mm X 50mm X 1 C | 53 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ORC 26101605</t>
+  </si>
+  <si>
+    <t>GREGÓRIO'S</t>
+  </si>
+  <si>
+    <t>JOSÉ KOURY</t>
+  </si>
+  <si>
+    <t>ETIQ 30mm X 10mm X 3 C | 21,667 M  c/ 5000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26101901</t>
+  </si>
+  <si>
+    <t>ORC 26101902</t>
+  </si>
+  <si>
+    <t>VESTA</t>
+  </si>
+  <si>
+    <t>ROT 45mm X 98mm X 1 C | 40 M  c/ 400 ROT</t>
+  </si>
+  <si>
+    <t>ORC 26102004</t>
+  </si>
+  <si>
+    <t>CASA MAGALHAES AUTOMACAO LTDA.</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 80mm X 1 C | 28 M  c/ 350 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 150mm X 1 C | 31 M  c/ 200 ETIQ</t>
+  </si>
+  <si>
+    <t>ROT 90mm X 40mm X 1 C | 43 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ETIQ 15mm X 28mm X 3 C | 52 M  c/ 5010 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26102005</t>
+  </si>
+  <si>
+    <t>DOMINGOS FRANCIULLI</t>
+  </si>
+  <si>
+    <t>ROT 100mm X 150mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ORC 26102008</t>
+  </si>
+  <si>
+    <t>BELINELLI</t>
+  </si>
+  <si>
+    <t>ROT 38mm X 38mm X 2 C | 41 M  c/ 1070 ROT</t>
+  </si>
+  <si>
+    <t>ORC 26102202</t>
+  </si>
+  <si>
+    <t>99 FOOD</t>
+  </si>
+  <si>
+    <t>ETIQ 45mm X 98mm X 1 C | 40,7 M  c/ 400 ETIQ</t>
+  </si>
+  <si>
+    <t>FASSON VINIL BRANCO FOSCO 100/DFAM485/80G</t>
+  </si>
+  <si>
+    <t>ORC 26102203</t>
+  </si>
+  <si>
+    <t>ETIQ 35mm X 90mm X 1 C | 37,3 M  c/ 400 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26102206</t>
+  </si>
+  <si>
+    <t>UNIMARKA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 40mm X 1 C | 80 M  c/ 1860 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 75mm X 1 C | 78 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ROT 100mm X 75mm X 1 C | 78 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ORC 26102302</t>
+  </si>
+  <si>
+    <t>KAROLAYNE BATISTA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 150mm X 1 C | 76,5 M  c/ 500 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26102303</t>
+  </si>
+  <si>
+    <t>SYNKKA PLANT NUTRITION LTDA.</t>
+  </si>
+  <si>
+    <t>ETIQ 130mm X 258mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ETIQ 126mm X 150mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ETIQ 133mm X 190mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ORC 26102304</t>
+  </si>
+  <si>
+    <t>COCA-COLA</t>
+  </si>
+  <si>
+    <t>ETIQ 70mm X 100mm X 1 C | 10,5 M  c/ 100 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 105mm X 148mm X 1 C | 314 M  c/ 2000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26102601</t>
+  </si>
+  <si>
+    <t>ABROFOL FERTILIZANTES LTDA</t>
+  </si>
+  <si>
+    <t>ROT 140mm X 275mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ORC 26102602</t>
+  </si>
+  <si>
+    <t>BRASILQUIMICA INDUSTRAI E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>ROT 140mm X 220mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ORC 26102702</t>
+  </si>
+  <si>
+    <t>RAZÃO SOCIAL: J L HIDRACON ARTEFATOS DE CIMENTO LTDA</t>
+  </si>
+  <si>
+    <t>ORC 26102703</t>
+  </si>
+  <si>
     <t>WALDENIR</t>
   </si>
   <si>
-    <t>ORC 26100904</t>
-  </si>
-  <si>
-    <t>ORC 26100905</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 150mm X 1 C | 157 M  c/ 1040 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 90mm X 50mm X 1 C | 40 M  c/ 800 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26101301</t>
-  </si>
-  <si>
-    <t>DOMART ALIMENTOS</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>ETIQ 50mm X 53mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 150mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ETIQ 80mm X 65mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ETIQ 85mm X 65mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ETIQ 60mm X 60mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>MIG SUPERMERCADOS – ATACADO E VAREJO</t>
-  </si>
-  <si>
-    <t>ROT 65mm X 65mm X 1 C | 68 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ORC 26101302</t>
-  </si>
-  <si>
-    <t>ETIQ 150mm X 200mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ORC 26101401</t>
-  </si>
-  <si>
-    <t>DOMART ALIMENTOS LTDA.</t>
-  </si>
-  <si>
-    <t>ETIQ 120mm X 200mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ETIQ 120mm X 170mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ORC 26101402</t>
-  </si>
-  <si>
-    <t>ROT 65mm X 89mm X 1 C | 92 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ROT 80mm X 82mm X 1 C | 85 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ROT 79,5mm X 90mm X 1 C | 93 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ROT 58mm X 85mm X 1 C | 88 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ORC 26101405</t>
-  </si>
-  <si>
-    <t>CATABY INDÚSTRIA E COMÉRCIO DE CARNES LTDA</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>ROT 165mm X 75mm X 1 C | 312 M  c/ 4000 ROT</t>
-  </si>
-  <si>
-    <t>ETIQ 30mm X 120mm X 1 C | 492 M  c/ 4000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26101410</t>
-  </si>
-  <si>
-    <t>SUPERMERCADOS DALBEN LTDA</t>
-  </si>
-  <si>
-    <t>ROT 85mm X 135mm X 1 C | 69 M  c/ 500 ROT</t>
-  </si>
-  <si>
-    <t>ROT 145mm X 120mm X 1 C | 61,5 M  c/ 500 ROT</t>
-  </si>
-  <si>
-    <t>ETIQ 50mm X 50mm X  C | 53 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26101411</t>
-  </si>
-  <si>
-    <t>POINT CLEAN IND E COM PROD DE LIMPEZA LTDA-ME</t>
-  </si>
-  <si>
-    <t>ROT 120mm X 100mm X 1 C | 103 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ETIQ 140mm X 120mm X 1 C | 123 M  c/ 1020 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 145mm X 125mm X 1 C | 128 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 110mm X 180mm X 1 C | 183 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26101501</t>
-  </si>
-  <si>
-    <t>CARLOS A H BORGES </t>
-  </si>
-  <si>
-    <t>ETIQ 70mm X 40mm X 1 C | 35 M  c/ 810 ETIQ</t>
-  </si>
-  <si>
-    <t>A.42 BOPP Branco Fosco</t>
-  </si>
-  <si>
-    <t>ORC 26101503</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO MUNHOZ  </t>
-  </si>
-  <si>
-    <t>ROT 80mm X 60mm X 1 C | 63 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ORC 26101505</t>
-  </si>
-  <si>
-    <t>PANIFICADORA BONJARDIM</t>
-  </si>
-  <si>
-    <t>EDEVALDO</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 40mm X 1 C | 43 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26101510</t>
-  </si>
-  <si>
-    <t>FERNANDO BARTOLOMEU</t>
-  </si>
-  <si>
-    <t>LUIZ FREITAS</t>
-  </si>
-  <si>
-    <t>ORC 26101512</t>
-  </si>
-  <si>
-    <t>M MAXI RANCHO</t>
-  </si>
-  <si>
-    <t>ROT 60mm X 75mm X 1 C | 78 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ETIQ 60mm X 75mm X 1 C | 78 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26101601</t>
-  </si>
-  <si>
-    <t>SAGE BRASIL INTERIORES AUTO. IND. E COM. LTDA</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 75mm X 1 C | 131,1 M  c/ 1680 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 50mm X 42mm X 1 C | 90 M  c/ 2000 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 60mm X 15mm X 1 C | 58,68 M  c/ 3260 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 110mm X 180mm X 1 C | 90 M  c/ 490 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26101602</t>
-  </si>
-  <si>
-    <t>ROGÉRIO FRANCISCO DA SILVA</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 120mm X 1 C | 60 M  c/ 500 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 101mm X 54mm X 1 C | 9,5 M  c/ 170 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26101603</t>
-  </si>
-  <si>
-    <t>MIG ATACADO E VAREJO LTDA</t>
-  </si>
-  <si>
-    <t>ROT 50mm X 50mm X 1 C | 53 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ORC 26101605</t>
-  </si>
-  <si>
-    <t>GREGÓRIO'S</t>
-  </si>
-  <si>
-    <t>JOSÉ KOURY</t>
-  </si>
-  <si>
-    <t>ETIQ 30mm X 10mm X 3 C | 21,667 M  c/ 5000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26101901</t>
-  </si>
-  <si>
-    <t>ORC 26101902</t>
-  </si>
-  <si>
-    <t>VESTA</t>
-  </si>
-  <si>
-    <t>ROT 45mm X 98mm X 1 C | 40 M  c/ 400 ROT</t>
-  </si>
-  <si>
-    <t>ORC 26102004</t>
-  </si>
-  <si>
-    <t>CASA MAGALHAES AUTOMACAO LTDA.</t>
-  </si>
-  <si>
-    <t>CE</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 80mm X 1 C | 28 M  c/ 350 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 150mm X 1 C | 31 M  c/ 200 ETIQ</t>
-  </si>
-  <si>
-    <t>ROT 90mm X 40mm X 1 C | 43 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ETIQ 15mm X 28mm X 3 C | 52 M  c/ 5010 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26102005</t>
-  </si>
-  <si>
-    <t>DOMINGOS FRANCIULLI</t>
-  </si>
-  <si>
-    <t>ROT 100mm X 150mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ORC 26102008</t>
-  </si>
-  <si>
-    <t>BELINELLI</t>
-  </si>
-  <si>
-    <t>ROT 38mm X 38mm X 2 C | 41 M  c/ 1070 ROT</t>
-  </si>
-  <si>
-    <t>ORC 26102202</t>
-  </si>
-  <si>
-    <t>99 FOOD</t>
-  </si>
-  <si>
-    <t>ETIQ 45mm X 98mm X 1 C | 40,7 M  c/ 400 ETIQ</t>
-  </si>
-  <si>
-    <t>FASSON VINIL BRANCO FOSCO 100/DFAM485/80G</t>
-  </si>
-  <si>
-    <t>ORC 26102203</t>
-  </si>
-  <si>
-    <t>ETIQ 35mm X 90mm X 1 C | 37,3 M  c/ 400 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26102206</t>
-  </si>
-  <si>
-    <t>UNIMARKA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 40mm X 1 C | 80 M  c/ 1860 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 75mm X 1 C | 78 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ROT 100mm X 75mm X 1 C | 78 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ORC 26102302</t>
-  </si>
-  <si>
-    <t>KAROLAYNE BATISTA DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 150mm X 1 C | 76,5 M  c/ 500 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26102303</t>
-  </si>
-  <si>
-    <t>SYNKKA PLANT NUTRITION LTDA.</t>
-  </si>
-  <si>
-    <t>ETIQ 130mm X 258mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ETIQ 126mm X 150mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ETIQ 133mm X 190mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ORC 26102304</t>
-  </si>
-  <si>
-    <t>COCA-COLA</t>
-  </si>
-  <si>
-    <t>ETIQ 70mm X 100mm X 1 C | 10,5 M  c/ 100 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 105mm X 148mm X 1 C | 314 M  c/ 2000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26102305</t>
+    <t>ETIQ 60mm X 60mm X 1 C | 63 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26102704</t>
   </si>
   <si>
     <t>J F INDUSTRIA DE COSMETICOS LTDA</t>
   </si>
   <si>
+    <t>ROT 80mm X 115mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ORC 26102705</t>
+  </si>
+  <si>
+    <t>RED BOI</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 75mm X 1 C | 38 M  c/ 500 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26102801</t>
+  </si>
+  <si>
     <t>ROT 83mm X 67mm X 1 C | METRAGEM A DEFINIR</t>
   </si>
   <si>
-    <t>ORC 26102306</t>
+    <t>SERRA AZUL WATER PARK (WETN WILD)</t>
+  </si>
+  <si>
+    <t>TAG 55mm X 89mm X 1 C | 90 M  c/ 1000 TAG</t>
+  </si>
+  <si>
+    <t>R 16 Papel Termoticket 167 gr/m²</t>
+  </si>
+  <si>
+    <t>ORC 26102803</t>
   </si>
   <si>
     <t>ROT 110mm X 200mm X 1 C | METRAGEM A DEFINIR</t>
   </si>
   <si>
-    <t>ROT 80mm X 115mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
     <t>ROT 135mm X 70mm X 1 C | METRAGEM A DEFINIR</t>
   </si>
   <si>
     <t>ETIQ 135mm X 70mm X 1 C | METRAGEM A DEFINIR</t>
   </si>
   <si>
-    <t>ORC 26102601</t>
-  </si>
-  <si>
-    <t>ABROFOL FERTILIZANTES LTDA</t>
-  </si>
-  <si>
-    <t>ROT 140mm X 275mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ORC 26102602</t>
-  </si>
-  <si>
-    <t>BRASILQUIMICA INDUSTRAI E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>ROT 140mm X 220mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ORC 26102701</t>
+    <t>ORC 26102807</t>
+  </si>
+  <si>
+    <t>SUPERMERCADOS PLANALTO</t>
+  </si>
+  <si>
+    <t>ROT 95mm X 67mm X 1 C | 70 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ORC 26102808</t>
+  </si>
+  <si>
+    <t>ROT 100mm X 21mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ORC 26102810</t>
   </si>
   <si>
     <t>REI DO BOI INDÚSTRIA E DISTRUIDORA DE CARNES LTDA.</t>
@@ -1850,31 +1892,16 @@
     <t>ETIQ 120,06mm X 130,45mm X 1 C | METRAGEM A DEFINIR</t>
   </si>
   <si>
-    <t>ORC 26102702</t>
-  </si>
-  <si>
-    <t>RAZÃO SOCIAL: J L HIDRACON ARTEFATOS DE CIMENTO LTDA</t>
-  </si>
-  <si>
-    <t>DANIELA LIMA</t>
-  </si>
-  <si>
-    <t>ORC 26102703</t>
-  </si>
-  <si>
-    <t>ETIQ 60mm X 60mm X 1 C | 63 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26102704</t>
-  </si>
-  <si>
-    <t>ORC 26102705</t>
-  </si>
-  <si>
-    <t>RED BOI</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 75mm X 1 C | 38 M  c/ 500 ETIQ</t>
+    <t>ORC 26102902</t>
+  </si>
+  <si>
+    <t>MORIFARMA</t>
+  </si>
+  <si>
+    <t>FLAVIO ENOBI</t>
+  </si>
+  <si>
+    <t>ETIQ 40mm X 55mm X 1 C | 29,5 M  c/ 500 ETIQ</t>
   </si>
 </sst>
 </file>
@@ -2253,7 +2280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11F50A2-59B7-40EA-83B4-B037F03CA50A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7448CB2-B847-4552-97F9-A18F51A2D626}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:X390"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2266,10 +2293,10 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1">
-        <v>861989.96999999986</v>
+        <v>863434.21000000008</v>
       </c>
       <c r="R1" s="1">
-        <v>15941321.028333338</v>
+        <v>15969263.971666671</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
@@ -2424,34 +2451,34 @@
         <v>20</v>
       </c>
       <c r="I4" s="3">
-        <v>145.75</v>
+        <v>156.72</v>
       </c>
       <c r="J4" s="3">
-        <v>2914.93</v>
+        <v>3134.47</v>
       </c>
       <c r="K4">
         <v>30</v>
       </c>
       <c r="L4" s="3">
-        <v>122.66</v>
+        <v>132.16</v>
       </c>
       <c r="M4" s="3">
-        <v>3679.88</v>
+        <v>3964.79</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4" s="3">
-        <v>111.5</v>
+        <v>120.29</v>
       </c>
       <c r="P4" s="3">
-        <v>4460.13</v>
+        <v>4811.66</v>
       </c>
       <c r="Q4" s="1">
-        <v>2914.93</v>
+        <v>3134.47</v>
       </c>
       <c r="R4" s="1">
-        <v>3684.9799999999996</v>
+        <v>3970.3066666666668</v>
       </c>
       <c r="S4" t="s">
         <v>30</v>
@@ -2490,34 +2517,34 @@
         <v>85</v>
       </c>
       <c r="I5" s="3">
-        <v>40.07</v>
+        <v>42.61</v>
       </c>
       <c r="J5" s="3">
-        <v>3405.76</v>
+        <v>3621.97</v>
       </c>
       <c r="K5">
         <v>115</v>
       </c>
       <c r="L5" s="3">
-        <v>34.99</v>
+        <v>37.340000000000003</v>
       </c>
       <c r="M5" s="3">
-        <v>4024.02</v>
+        <v>4294.18</v>
       </c>
       <c r="N5">
         <v>155</v>
       </c>
       <c r="O5" s="3">
-        <v>30.91</v>
+        <v>33.08</v>
       </c>
       <c r="P5" s="3">
-        <v>4791.32</v>
+        <v>5127.91</v>
       </c>
       <c r="Q5" s="1">
-        <v>3405.76</v>
+        <v>3621.97</v>
       </c>
       <c r="R5" s="1">
-        <v>4073.7000000000003</v>
+        <v>4348.0199999999995</v>
       </c>
       <c r="S5" t="s">
         <v>30</v>
@@ -2622,34 +2649,34 @@
         <v>65</v>
       </c>
       <c r="I7" s="3">
-        <v>40.04</v>
+        <v>42.99</v>
       </c>
       <c r="J7" s="3">
-        <v>2602.66</v>
+        <v>2794.47</v>
       </c>
       <c r="K7">
         <v>90</v>
       </c>
       <c r="L7" s="3">
-        <v>35.979999999999997</v>
+        <v>38.72</v>
       </c>
       <c r="M7" s="3">
-        <v>3238.28</v>
+        <v>3484.45</v>
       </c>
       <c r="N7">
         <v>120</v>
       </c>
       <c r="O7" s="3">
-        <v>32.67</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="P7" s="3">
-        <v>3919.81</v>
+        <v>4224.2</v>
       </c>
       <c r="Q7" s="1">
-        <v>2602.66</v>
+        <v>2794.47</v>
       </c>
       <c r="R7" s="1">
-        <v>3253.5833333333335</v>
+        <v>3501.0399999999995</v>
       </c>
       <c r="S7" t="s">
         <v>47</v>
@@ -2685,34 +2712,34 @@
         <v>72</v>
       </c>
       <c r="I8" s="3">
-        <v>43.9</v>
+        <v>44.43</v>
       </c>
       <c r="J8" s="3">
-        <v>3160.99</v>
+        <v>3199.08</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>40.06</v>
+        <v>40.54</v>
       </c>
       <c r="M8" s="3">
-        <v>4006.17</v>
+        <v>4054.46</v>
       </c>
       <c r="N8">
         <v>144</v>
       </c>
       <c r="O8" s="3">
-        <v>37.700000000000003</v>
+        <v>38.159999999999997</v>
       </c>
       <c r="P8" s="3">
-        <v>5428.92</v>
+        <v>5494.35</v>
       </c>
       <c r="Q8" s="1">
-        <v>3160.99</v>
+        <v>3199.08</v>
       </c>
       <c r="R8" s="1">
-        <v>4198.6933333333336</v>
+        <v>4249.2966666666662</v>
       </c>
       <c r="S8" t="s">
         <v>53</v>
@@ -3991,34 +4018,34 @@
         <v>25</v>
       </c>
       <c r="I30" s="3">
-        <v>310.44</v>
+        <v>314.91000000000003</v>
       </c>
       <c r="J30" s="3">
-        <v>7761.11</v>
+        <v>7872.66</v>
       </c>
       <c r="K30">
         <v>35</v>
       </c>
       <c r="L30" s="3">
-        <v>275.43</v>
+        <v>279.52999999999997</v>
       </c>
       <c r="M30" s="3">
-        <v>9640.14</v>
+        <v>9783.41</v>
       </c>
       <c r="N30">
         <v>50</v>
       </c>
       <c r="O30" s="3">
-        <v>245.94</v>
+        <v>249.7</v>
       </c>
       <c r="P30" s="3">
-        <v>12296.97</v>
+        <v>12484.89</v>
       </c>
       <c r="Q30" s="1">
-        <v>7761.11</v>
+        <v>7872.66</v>
       </c>
       <c r="R30" s="1">
-        <v>9899.4066666666677</v>
+        <v>10046.986666666666</v>
       </c>
       <c r="S30" t="s">
         <v>47</v>
@@ -4610,34 +4637,34 @@
         <v>15</v>
       </c>
       <c r="I41" s="3">
-        <v>198.57</v>
+        <v>200.42</v>
       </c>
       <c r="J41" s="3">
-        <v>2978.6</v>
+        <v>3006.36</v>
       </c>
       <c r="K41">
         <v>20</v>
       </c>
       <c r="L41" s="3">
-        <v>166.75</v>
+        <v>168.37</v>
       </c>
       <c r="M41" s="3">
-        <v>3335.08</v>
+        <v>3367.32</v>
       </c>
       <c r="N41">
         <v>30</v>
       </c>
       <c r="O41" s="3">
-        <v>144.37</v>
+        <v>145.85</v>
       </c>
       <c r="P41" s="3">
-        <v>4331.1899999999996</v>
+        <v>4375.6000000000004</v>
       </c>
       <c r="Q41" s="1">
-        <v>2978.6</v>
+        <v>3006.36</v>
       </c>
       <c r="R41" s="1">
-        <v>3548.2899999999995</v>
+        <v>3583.0933333333337</v>
       </c>
       <c r="S41" t="s">
         <v>30</v>
@@ -4676,34 +4703,34 @@
         <v>15</v>
       </c>
       <c r="I42" s="3">
-        <v>224.21</v>
+        <v>226.3</v>
       </c>
       <c r="J42" s="3">
-        <v>3363.09</v>
+        <v>3394.51</v>
       </c>
       <c r="K42">
         <v>20</v>
       </c>
       <c r="L42" s="3">
-        <v>197.15</v>
+        <v>199.08</v>
       </c>
       <c r="M42" s="3">
-        <v>3942.93</v>
+        <v>3981.54</v>
       </c>
       <c r="N42">
         <v>30</v>
       </c>
       <c r="O42" s="3">
-        <v>166.44</v>
+        <v>168.16</v>
       </c>
       <c r="P42" s="3">
-        <v>4993.33</v>
+        <v>5044.78</v>
       </c>
       <c r="Q42" s="1">
-        <v>3363.09</v>
+        <v>3394.51</v>
       </c>
       <c r="R42" s="1">
-        <v>4099.7833333333338</v>
+        <v>4140.2766666666666</v>
       </c>
       <c r="S42" t="s">
         <v>30</v>
@@ -4742,34 +4769,34 @@
         <v>15</v>
       </c>
       <c r="I43" s="3">
-        <v>240.19</v>
+        <v>242.44</v>
       </c>
       <c r="J43" s="3">
-        <v>3602.91</v>
+        <v>3636.67</v>
       </c>
       <c r="K43">
         <v>20</v>
       </c>
       <c r="L43" s="3">
-        <v>206.86</v>
+        <v>208.88</v>
       </c>
       <c r="M43" s="3">
-        <v>4137.2700000000004</v>
+        <v>4177.68</v>
       </c>
       <c r="N43">
         <v>30</v>
       </c>
       <c r="O43" s="3">
-        <v>180.07</v>
+        <v>181.93</v>
       </c>
       <c r="P43" s="3">
-        <v>5402.01</v>
+        <v>5457.86</v>
       </c>
       <c r="Q43" s="1">
-        <v>3602.91</v>
+        <v>3636.67</v>
       </c>
       <c r="R43" s="1">
-        <v>4380.7300000000005</v>
+        <v>4424.07</v>
       </c>
       <c r="S43" t="s">
         <v>30</v>
@@ -4808,34 +4835,34 @@
         <v>25</v>
       </c>
       <c r="I44" s="3">
-        <v>165.1</v>
+        <v>166.66</v>
       </c>
       <c r="J44" s="3">
-        <v>4127.6000000000004</v>
+        <v>4166.5200000000004</v>
       </c>
       <c r="K44">
         <v>35</v>
       </c>
       <c r="L44" s="3">
-        <v>139.44</v>
+        <v>140.82</v>
       </c>
       <c r="M44" s="3">
-        <v>4880.43</v>
+        <v>4928.67</v>
       </c>
       <c r="N44">
         <v>50</v>
       </c>
       <c r="O44" s="3">
-        <v>122.56</v>
+        <v>123.83</v>
       </c>
       <c r="P44" s="3">
-        <v>6127.97</v>
+        <v>6191.47</v>
       </c>
       <c r="Q44" s="1">
-        <v>4127.6000000000004</v>
+        <v>4166.5200000000004</v>
       </c>
       <c r="R44" s="1">
-        <v>5045.333333333333</v>
+        <v>5095.5533333333333</v>
       </c>
       <c r="S44" t="s">
         <v>30</v>
@@ -4874,34 +4901,34 @@
         <v>20</v>
       </c>
       <c r="I45" s="3">
-        <v>190.54</v>
+        <v>192.3</v>
       </c>
       <c r="J45" s="3">
-        <v>3810.76</v>
+        <v>3845.96</v>
       </c>
       <c r="K45">
         <v>30</v>
       </c>
       <c r="L45" s="3">
-        <v>156.61000000000001</v>
+        <v>158.15</v>
       </c>
       <c r="M45" s="3">
-        <v>4698.24</v>
+        <v>4744.38</v>
       </c>
       <c r="N45">
         <v>40</v>
       </c>
       <c r="O45" s="3">
-        <v>139.04</v>
+        <v>140.44999999999999</v>
       </c>
       <c r="P45" s="3">
-        <v>5561.42</v>
+        <v>5618.19</v>
       </c>
       <c r="Q45" s="1">
-        <v>3810.76</v>
+        <v>3845.96</v>
       </c>
       <c r="R45" s="1">
-        <v>4690.1400000000003</v>
+        <v>4736.1766666666663</v>
       </c>
       <c r="S45" t="s">
         <v>30</v>
@@ -5354,34 +5381,34 @@
         <v>90</v>
       </c>
       <c r="I53" s="3">
-        <v>36.36</v>
+        <v>36.97</v>
       </c>
       <c r="J53" s="3">
-        <v>3272.71</v>
+        <v>3326.89</v>
       </c>
       <c r="K53">
         <v>120</v>
       </c>
       <c r="L53" s="3">
-        <v>32.630000000000003</v>
+        <v>33.18</v>
       </c>
       <c r="M53" s="3">
-        <v>3915.03</v>
+        <v>3981.56</v>
       </c>
       <c r="N53">
         <v>160</v>
       </c>
       <c r="O53" s="3">
-        <v>29.8</v>
+        <v>30.32</v>
       </c>
       <c r="P53" s="3">
-        <v>4767.6899999999996</v>
+        <v>4850.5200000000004</v>
       </c>
       <c r="Q53" s="1">
-        <v>3272.71</v>
+        <v>3326.89</v>
       </c>
       <c r="R53" s="1">
-        <v>3985.1433333333334</v>
+        <v>4052.9900000000002</v>
       </c>
       <c r="S53" t="s">
         <v>53</v>
@@ -5396,7 +5423,7 @@
         <v>176</v>
       </c>
       <c r="B54" s="2">
-        <v>46255.715358796297</v>
+        <v>46323.653310185182</v>
       </c>
       <c r="C54" t="s">
         <v>177</v>
@@ -5453,7 +5480,7 @@
         <v>176</v>
       </c>
       <c r="B55" s="2">
-        <v>46255.715358796297</v>
+        <v>46323.653310185182</v>
       </c>
       <c r="C55" t="s">
         <v>177</v>
@@ -5510,7 +5537,7 @@
         <v>181</v>
       </c>
       <c r="B56" s="2">
-        <v>46255.705381944441</v>
+        <v>46323.652916666666</v>
       </c>
       <c r="C56" t="s">
         <v>182</v>
@@ -5567,7 +5594,7 @@
         <v>181</v>
       </c>
       <c r="B57" s="2">
-        <v>46255.705381944441</v>
+        <v>46323.652916666666</v>
       </c>
       <c r="C57" t="s">
         <v>182</v>
@@ -7301,7 +7328,7 @@
         <v>256</v>
       </c>
       <c r="B88" s="2">
-        <v>46262.725381944445</v>
+        <v>46323.654189814813</v>
       </c>
       <c r="C88" t="s">
         <v>257</v>
@@ -8456,10 +8483,10 @@
         <v>300</v>
       </c>
       <c r="I107" s="3">
-        <v>14.5</v>
+        <v>14.27</v>
       </c>
       <c r="J107" s="3">
-        <v>4350</v>
+        <v>4281</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -8480,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="Q107" s="1">
-        <v>4350</v>
+        <v>4281</v>
       </c>
       <c r="R107" s="1">
-        <v>4350</v>
+        <v>4281</v>
       </c>
       <c r="S107" t="s">
         <v>53</v>
@@ -8708,34 +8735,34 @@
         <v>220</v>
       </c>
       <c r="I111" s="3">
-        <v>19.309999999999999</v>
+        <v>21.65</v>
       </c>
       <c r="J111" s="3">
-        <v>4248.2</v>
+        <v>4763</v>
       </c>
       <c r="K111">
         <v>350</v>
       </c>
       <c r="L111" s="3">
-        <v>14.57</v>
+        <v>16.46</v>
       </c>
       <c r="M111" s="3">
-        <v>5099.5</v>
+        <v>5761</v>
       </c>
       <c r="N111">
         <v>525</v>
       </c>
       <c r="O111" s="3">
-        <v>11.4</v>
+        <v>12.96</v>
       </c>
       <c r="P111" s="3">
-        <v>5985</v>
+        <v>6804</v>
       </c>
       <c r="Q111" s="1">
-        <v>4248.2</v>
+        <v>4763</v>
       </c>
       <c r="R111" s="1">
-        <v>4350</v>
+        <v>4281</v>
       </c>
       <c r="S111" t="s">
         <v>53</v>
@@ -9950,7 +9977,7 @@
         <v>346</v>
       </c>
       <c r="B131" s="2">
-        <v>46287.644872685189</v>
+        <v>46323.655046296299</v>
       </c>
       <c r="C131" t="s">
         <v>347</v>
@@ -10823,7 +10850,7 @@
         <v>379</v>
       </c>
       <c r="B146" s="2">
-        <v>46295.662303240744</v>
+        <v>46323.65552083333</v>
       </c>
       <c r="C146" t="s">
         <v>380</v>
@@ -10832,10 +10859,10 @@
         <v>258</v>
       </c>
       <c r="E146" t="s">
-        <v>178</v>
+        <v>381</v>
       </c>
       <c r="F146" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G146" t="s">
         <v>73</v>
@@ -10880,7 +10907,7 @@
         <v>379</v>
       </c>
       <c r="B147" s="2">
-        <v>46295.662303240744</v>
+        <v>46323.65552083333</v>
       </c>
       <c r="C147" t="s">
         <v>380</v>
@@ -10889,10 +10916,10 @@
         <v>258</v>
       </c>
       <c r="E147" t="s">
-        <v>178</v>
+        <v>381</v>
       </c>
       <c r="F147" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G147" t="s">
         <v>36</v>
@@ -10937,7 +10964,7 @@
         <v>379</v>
       </c>
       <c r="B148" s="2">
-        <v>46295.662303240744</v>
+        <v>46323.65552083333</v>
       </c>
       <c r="C148" t="s">
         <v>380</v>
@@ -10946,10 +10973,10 @@
         <v>258</v>
       </c>
       <c r="E148" t="s">
-        <v>178</v>
+        <v>381</v>
       </c>
       <c r="F148" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G148" t="s">
         <v>67</v>
@@ -10991,22 +11018,22 @@
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B149" s="2">
         <v>46295.662824074076</v>
       </c>
       <c r="C149" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D149" t="s">
         <v>258</v>
       </c>
       <c r="E149" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F149" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G149" t="s">
         <v>36</v>
@@ -11048,22 +11075,22 @@
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B150" s="2">
         <v>46295.662824074076</v>
       </c>
       <c r="C150" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D150" t="s">
         <v>258</v>
       </c>
       <c r="E150" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F150" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G150" t="s">
         <v>67</v>
@@ -11105,22 +11132,22 @@
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B151" s="2">
         <v>46295.662824074076</v>
       </c>
       <c r="C151" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D151" t="s">
         <v>258</v>
       </c>
       <c r="E151" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F151" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G151" t="s">
         <v>36</v>
@@ -11162,22 +11189,22 @@
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B152" s="2">
         <v>46295.662824074076</v>
       </c>
       <c r="C152" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D152" t="s">
         <v>258</v>
       </c>
       <c r="E152" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F152" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G152" t="s">
         <v>36</v>
@@ -11219,22 +11246,22 @@
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B153" s="2">
         <v>46295.662824074076</v>
       </c>
       <c r="C153" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D153" t="s">
         <v>258</v>
       </c>
       <c r="E153" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F153" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G153" t="s">
         <v>67</v>
@@ -11276,22 +11303,22 @@
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B154" s="2">
         <v>46295.660590277781</v>
       </c>
       <c r="C154" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D154" t="s">
         <v>258</v>
       </c>
       <c r="E154" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F154" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G154" t="s">
         <v>36</v>
@@ -11333,22 +11360,22 @@
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B155" s="2">
         <v>46295.660590277781</v>
       </c>
       <c r="C155" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D155" t="s">
         <v>258</v>
       </c>
       <c r="E155" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F155" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G155" t="s">
         <v>67</v>
@@ -11390,22 +11417,22 @@
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B156" s="2">
         <v>46295.660590277781</v>
       </c>
       <c r="C156" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D156" t="s">
         <v>258</v>
       </c>
       <c r="E156" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F156" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G156" t="s">
         <v>67</v>
@@ -11447,25 +11474,25 @@
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B157" s="2">
         <v>46295.660590277781</v>
       </c>
       <c r="C157" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D157" t="s">
         <v>258</v>
       </c>
       <c r="E157" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F157" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G157" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H157">
         <v>130</v>
@@ -11504,13 +11531,13 @@
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B158" s="2">
         <v>46295.67895833333</v>
       </c>
       <c r="C158" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D158" t="s">
         <v>258</v>
@@ -11519,7 +11546,7 @@
         <v>141</v>
       </c>
       <c r="F158" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G158" t="s">
         <v>36</v>
@@ -11561,13 +11588,13 @@
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B159" s="2">
         <v>46295.67895833333</v>
       </c>
       <c r="C159" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D159" t="s">
         <v>258</v>
@@ -11576,7 +11603,7 @@
         <v>141</v>
       </c>
       <c r="F159" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G159" t="s">
         <v>73</v>
@@ -11618,13 +11645,13 @@
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B160" s="2">
         <v>46295.67895833333</v>
       </c>
       <c r="C160" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D160" t="s">
         <v>258</v>
@@ -11633,7 +11660,7 @@
         <v>141</v>
       </c>
       <c r="F160" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G160" t="s">
         <v>36</v>
@@ -11675,19 +11702,19 @@
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B161" s="2">
         <v>46295.671307870369</v>
       </c>
       <c r="C161" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D161" t="s">
         <v>258</v>
       </c>
       <c r="E161" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F161" t="s">
         <v>184</v>
@@ -11732,22 +11759,22 @@
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B162" s="2">
         <v>46295.671307870369</v>
       </c>
       <c r="C162" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D162" t="s">
         <v>258</v>
       </c>
       <c r="E162" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F162" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G162" t="s">
         <v>115</v>
@@ -11789,22 +11816,22 @@
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B163" s="2">
         <v>46295.671307870369</v>
       </c>
       <c r="C163" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D163" t="s">
         <v>258</v>
       </c>
       <c r="E163" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F163" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G163" t="s">
         <v>98</v>
@@ -11846,22 +11873,22 @@
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B164" s="2">
         <v>46295.671307870369</v>
       </c>
       <c r="C164" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D164" t="s">
         <v>258</v>
       </c>
       <c r="E164" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F164" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G164" t="s">
         <v>73</v>
@@ -11903,22 +11930,22 @@
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B165" s="2">
         <v>46295.671307870369</v>
       </c>
       <c r="C165" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D165" t="s">
         <v>258</v>
       </c>
       <c r="E165" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F165" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G165" t="s">
         <v>29</v>
@@ -11960,13 +11987,13 @@
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B166" s="2">
         <v>46296.652222222219</v>
       </c>
       <c r="C166" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D166" t="s">
         <v>60</v>
@@ -11975,7 +12002,7 @@
         <v>341</v>
       </c>
       <c r="F166" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G166" t="s">
         <v>201</v>
@@ -12023,7 +12050,7 @@
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B167" s="2">
         <v>46297.609618055554</v>
@@ -12038,7 +12065,7 @@
         <v>45</v>
       </c>
       <c r="F167" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G167" t="s">
         <v>36</v>
@@ -12072,22 +12099,22 @@
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B168" s="2">
         <v>46297.679155092592</v>
       </c>
       <c r="C168" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D168" t="s">
         <v>60</v>
       </c>
       <c r="E168" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F168" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G168" t="s">
         <v>73</v>
@@ -12129,22 +12156,22 @@
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B169" s="2">
         <v>46297.679155092592</v>
       </c>
       <c r="C169" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D169" t="s">
         <v>60</v>
       </c>
       <c r="E169" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F169" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G169" t="s">
         <v>67</v>
@@ -12186,22 +12213,22 @@
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B170" s="2">
         <v>46297.679155092592</v>
       </c>
       <c r="C170" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D170" t="s">
         <v>60</v>
       </c>
       <c r="E170" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F170" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G170" t="s">
         <v>73</v>
@@ -12243,13 +12270,13 @@
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B171" s="2">
         <v>46300.351354166669</v>
       </c>
       <c r="C171" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D171" t="s">
         <v>26</v>
@@ -12258,7 +12285,7 @@
         <v>65</v>
       </c>
       <c r="F171" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G171" t="s">
         <v>29</v>
@@ -12303,19 +12330,19 @@
         <v>31</v>
       </c>
       <c r="U171" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="V171" s="2"/>
     </row>
     <row r="172" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B172" s="2">
         <v>46300.35019675926</v>
       </c>
       <c r="C172" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D172" t="s">
         <v>26</v>
@@ -12324,7 +12351,7 @@
         <v>65</v>
       </c>
       <c r="F172" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G172" t="s">
         <v>102</v>
@@ -12372,13 +12399,13 @@
     </row>
     <row r="173" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B173" s="2">
         <v>46300.356377314813</v>
       </c>
       <c r="C173" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D173" t="s">
         <v>248</v>
@@ -12387,7 +12414,7 @@
         <v>294</v>
       </c>
       <c r="F173" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G173" t="s">
         <v>36</v>
@@ -12429,13 +12456,13 @@
     </row>
     <row r="174" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B174" s="2">
-        <v>46300.359131944446</v>
+        <v>46323.655752314815</v>
       </c>
       <c r="C174" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D174" t="s">
         <v>125</v>
@@ -12444,7 +12471,7 @@
         <v>178</v>
       </c>
       <c r="F174" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G174" t="s">
         <v>36</v>
@@ -12486,22 +12513,22 @@
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B175" s="2">
         <v>46300.473171296297</v>
       </c>
       <c r="C175" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D175" t="s">
         <v>262</v>
       </c>
       <c r="E175" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F175" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G175" t="s">
         <v>36</v>
@@ -12543,22 +12570,22 @@
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B176" s="2">
         <v>46300.473171296297</v>
       </c>
       <c r="C176" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D176" t="s">
         <v>262</v>
       </c>
       <c r="E176" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F176" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G176" t="s">
         <v>36</v>
@@ -12600,13 +12627,13 @@
     </row>
     <row r="177" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B177" s="2">
         <v>46300.631435185183</v>
       </c>
       <c r="C177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D177" t="s">
         <v>26</v>
@@ -12615,7 +12642,7 @@
         <v>174</v>
       </c>
       <c r="F177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G177" t="s">
         <v>36</v>
@@ -12657,13 +12684,13 @@
     </row>
     <row r="178" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B178" s="2">
         <v>46300.4137962963</v>
       </c>
       <c r="C178" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D178" t="s">
         <v>26</v>
@@ -12672,10 +12699,10 @@
         <v>120</v>
       </c>
       <c r="F178" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G178" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H178">
         <v>100</v>
@@ -12720,22 +12747,22 @@
     </row>
     <row r="179" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B179" s="2">
         <v>46300.472534722219</v>
       </c>
       <c r="C179" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D179" t="s">
         <v>262</v>
       </c>
       <c r="E179" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F179" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G179" t="s">
         <v>36</v>
@@ -12777,22 +12804,22 @@
     </row>
     <row r="180" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B180" s="2">
         <v>46300.55263888889</v>
       </c>
       <c r="C180" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D180" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E180" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F180" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G180" t="s">
         <v>52</v>
@@ -12834,13 +12861,13 @@
     </row>
     <row r="181" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B181" s="2">
         <v>46301.412546296298</v>
       </c>
       <c r="C181" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D181" t="s">
         <v>26</v>
@@ -12849,7 +12876,7 @@
         <v>263</v>
       </c>
       <c r="F181" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G181" t="s">
         <v>36</v>
@@ -12891,22 +12918,22 @@
     </row>
     <row r="182" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B182" s="2">
         <v>46301.510717592595</v>
       </c>
       <c r="C182" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D182" t="s">
         <v>262</v>
       </c>
       <c r="E182" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F182" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G182" t="s">
         <v>36</v>
@@ -12948,13 +12975,13 @@
     </row>
     <row r="183" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B183" s="2">
         <v>46303.389560185184</v>
       </c>
       <c r="C183" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D183" t="s">
         <v>125</v>
@@ -12963,10 +12990,10 @@
         <v>244</v>
       </c>
       <c r="F183" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G183" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H183">
         <v>60</v>
@@ -13005,13 +13032,13 @@
     </row>
     <row r="184" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B184" s="2">
         <v>46303.678877314815</v>
       </c>
       <c r="C184" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D184" t="s">
         <v>26</v>
@@ -13020,7 +13047,7 @@
         <v>65</v>
       </c>
       <c r="F184" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G184" t="s">
         <v>73</v>
@@ -13062,13 +13089,13 @@
     </row>
     <row r="185" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B185" s="2">
         <v>46304.360034722224</v>
       </c>
       <c r="C185" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D185" t="s">
         <v>262</v>
@@ -13077,7 +13104,7 @@
         <v>244</v>
       </c>
       <c r="F185" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G185" t="s">
         <v>269</v>
@@ -13119,10 +13146,10 @@
     </row>
     <row r="186" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B186" s="2">
-        <v>46304.690613425926</v>
+        <v>46323.658090277779</v>
       </c>
       <c r="C186" t="s">
         <v>371</v>
@@ -13131,7 +13158,7 @@
         <v>125</v>
       </c>
       <c r="E186" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="F186" t="s">
         <v>372</v>
@@ -13194,7 +13221,7 @@
         <v>268</v>
       </c>
       <c r="G187" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H187">
         <v>35</v>
@@ -13629,7 +13656,7 @@
         <v>474</v>
       </c>
       <c r="B195" s="2">
-        <v>46308.474664351852</v>
+        <v>46323.658541666664</v>
       </c>
       <c r="C195" t="s">
         <v>482</v>
@@ -13638,7 +13665,7 @@
         <v>125</v>
       </c>
       <c r="E195" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="F195" t="s">
         <v>483</v>
@@ -13752,7 +13779,7 @@
         <v>258</v>
       </c>
       <c r="E197" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F197" t="s">
         <v>488</v>
@@ -13809,7 +13836,7 @@
         <v>258</v>
       </c>
       <c r="E198" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F198" t="s">
         <v>489</v>
@@ -13857,7 +13884,7 @@
         <v>490</v>
       </c>
       <c r="B199" s="2">
-        <v>46309.420324074075</v>
+        <v>46323.658912037034</v>
       </c>
       <c r="C199" t="s">
         <v>482</v>
@@ -13866,7 +13893,7 @@
         <v>125</v>
       </c>
       <c r="E199" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="F199" t="s">
         <v>491</v>
@@ -13914,7 +13941,7 @@
         <v>490</v>
       </c>
       <c r="B200" s="2">
-        <v>46309.420324074075</v>
+        <v>46323.658912037034</v>
       </c>
       <c r="C200" t="s">
         <v>482</v>
@@ -13923,7 +13950,7 @@
         <v>125</v>
       </c>
       <c r="E200" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="F200" t="s">
         <v>492</v>
@@ -13971,7 +13998,7 @@
         <v>490</v>
       </c>
       <c r="B201" s="2">
-        <v>46309.420324074075</v>
+        <v>46323.658912037034</v>
       </c>
       <c r="C201" t="s">
         <v>482</v>
@@ -13980,7 +14007,7 @@
         <v>125</v>
       </c>
       <c r="E201" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="F201" t="s">
         <v>493</v>
@@ -14028,7 +14055,7 @@
         <v>490</v>
       </c>
       <c r="B202" s="2">
-        <v>46309.420324074075</v>
+        <v>46323.658912037034</v>
       </c>
       <c r="C202" t="s">
         <v>482</v>
@@ -14037,7 +14064,7 @@
         <v>125</v>
       </c>
       <c r="E202" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="F202" t="s">
         <v>494</v>
@@ -14085,7 +14112,7 @@
         <v>495</v>
       </c>
       <c r="B203" s="2">
-        <v>46309.639409722222</v>
+        <v>46323.650451388887</v>
       </c>
       <c r="C203" t="s">
         <v>496</v>
@@ -14094,10 +14121,10 @@
         <v>26</v>
       </c>
       <c r="E203" t="s">
+        <v>50</v>
+      </c>
+      <c r="F203" t="s">
         <v>497</v>
-      </c>
-      <c r="F203" t="s">
-        <v>498</v>
       </c>
       <c r="G203" t="s">
         <v>29</v>
@@ -14142,7 +14169,7 @@
         <v>495</v>
       </c>
       <c r="B204" s="2">
-        <v>46309.639409722222</v>
+        <v>46323.650451388887</v>
       </c>
       <c r="C204" t="s">
         <v>496</v>
@@ -14151,10 +14178,10 @@
         <v>26</v>
       </c>
       <c r="E204" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F204" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G204" t="s">
         <v>29</v>
@@ -14196,22 +14223,22 @@
     </row>
     <row r="205" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>499</v>
+      </c>
+      <c r="B205" s="2">
+        <v>46323.65079861111</v>
+      </c>
+      <c r="C205" t="s">
         <v>500</v>
-      </c>
-      <c r="B205" s="2">
-        <v>46309.657060185185</v>
-      </c>
-      <c r="C205" t="s">
-        <v>501</v>
       </c>
       <c r="D205" t="s">
         <v>26</v>
       </c>
       <c r="E205" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F205" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G205" t="s">
         <v>29</v>
@@ -14253,22 +14280,22 @@
     </row>
     <row r="206" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>499</v>
+      </c>
+      <c r="B206" s="2">
+        <v>46323.65079861111</v>
+      </c>
+      <c r="C206" t="s">
         <v>500</v>
-      </c>
-      <c r="B206" s="2">
-        <v>46309.657060185185</v>
-      </c>
-      <c r="C206" t="s">
-        <v>501</v>
       </c>
       <c r="D206" t="s">
         <v>26</v>
       </c>
       <c r="E206" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F206" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G206" t="s">
         <v>29</v>
@@ -14310,22 +14337,22 @@
     </row>
     <row r="207" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>499</v>
+      </c>
+      <c r="B207" s="2">
+        <v>46323.65079861111</v>
+      </c>
+      <c r="C207" t="s">
         <v>500</v>
-      </c>
-      <c r="B207" s="2">
-        <v>46309.657060185185</v>
-      </c>
-      <c r="C207" t="s">
-        <v>501</v>
       </c>
       <c r="D207" t="s">
         <v>26</v>
       </c>
       <c r="E207" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F207" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G207" t="s">
         <v>29</v>
@@ -14367,22 +14394,22 @@
     </row>
     <row r="208" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>504</v>
+      </c>
+      <c r="B208" s="2">
+        <v>46323.651087962964</v>
+      </c>
+      <c r="C208" t="s">
         <v>505</v>
-      </c>
-      <c r="B208" s="2">
-        <v>46309.659861111111</v>
-      </c>
-      <c r="C208" t="s">
-        <v>506</v>
       </c>
       <c r="D208" t="s">
         <v>26</v>
       </c>
       <c r="E208" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F208" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G208" t="s">
         <v>29</v>
@@ -14424,22 +14451,22 @@
     </row>
     <row r="209" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>504</v>
+      </c>
+      <c r="B209" s="2">
+        <v>46323.651087962964</v>
+      </c>
+      <c r="C209" t="s">
         <v>505</v>
-      </c>
-      <c r="B209" s="2">
-        <v>46309.659861111111</v>
-      </c>
-      <c r="C209" t="s">
-        <v>506</v>
       </c>
       <c r="D209" t="s">
         <v>26</v>
       </c>
       <c r="E209" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F209" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G209" t="s">
         <v>29</v>
@@ -14481,22 +14508,22 @@
     </row>
     <row r="210" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>504</v>
+      </c>
+      <c r="B210" s="2">
+        <v>46323.651087962964</v>
+      </c>
+      <c r="C210" t="s">
         <v>505</v>
-      </c>
-      <c r="B210" s="2">
-        <v>46309.659861111111</v>
-      </c>
-      <c r="C210" t="s">
-        <v>506</v>
       </c>
       <c r="D210" t="s">
         <v>26</v>
       </c>
       <c r="E210" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F210" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G210" t="s">
         <v>29</v>
@@ -14538,22 +14565,22 @@
     </row>
     <row r="211" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>504</v>
+      </c>
+      <c r="B211" s="2">
+        <v>46323.651087962964</v>
+      </c>
+      <c r="C211" t="s">
         <v>505</v>
-      </c>
-      <c r="B211" s="2">
-        <v>46309.659861111111</v>
-      </c>
-      <c r="C211" t="s">
-        <v>506</v>
       </c>
       <c r="D211" t="s">
         <v>26</v>
       </c>
       <c r="E211" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F211" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G211" t="s">
         <v>29</v>
@@ -14595,13 +14622,13 @@
     </row>
     <row r="212" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B212" s="2">
         <v>46310.409502314818</v>
       </c>
       <c r="C212" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D212" t="s">
         <v>70</v>
@@ -14610,10 +14637,10 @@
         <v>476</v>
       </c>
       <c r="F212" t="s">
+        <v>512</v>
+      </c>
+      <c r="G212" t="s">
         <v>513</v>
-      </c>
-      <c r="G212" t="s">
-        <v>514</v>
       </c>
       <c r="H212">
         <v>130</v>
@@ -14652,22 +14679,22 @@
     </row>
     <row r="213" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>514</v>
+      </c>
+      <c r="B213" s="2">
+        <v>46323.659444444442</v>
+      </c>
+      <c r="C213" t="s">
         <v>515</v>
-      </c>
-      <c r="B213" s="2">
-        <v>46310.412129629629</v>
-      </c>
-      <c r="C213" t="s">
-        <v>516</v>
       </c>
       <c r="D213" t="s">
         <v>125</v>
       </c>
       <c r="E213" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="F213" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G213" t="s">
         <v>29</v>
@@ -14709,22 +14736,22 @@
     </row>
     <row r="214" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>517</v>
+      </c>
+      <c r="B214" s="2">
+        <v>46323.650509259256</v>
+      </c>
+      <c r="C214" t="s">
         <v>518</v>
-      </c>
-      <c r="B214" s="2">
-        <v>46310.476678240739</v>
-      </c>
-      <c r="C214" t="s">
-        <v>519</v>
       </c>
       <c r="D214" t="s">
         <v>26</v>
       </c>
       <c r="E214" t="s">
-        <v>520</v>
+        <v>187</v>
       </c>
       <c r="F214" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G214" t="s">
         <v>36</v>
@@ -14766,19 +14793,19 @@
     </row>
     <row r="215" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B215" s="2">
         <v>46310.500497685185</v>
       </c>
       <c r="C215" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D215" t="s">
         <v>125</v>
       </c>
       <c r="E215" t="s">
-        <v>524</v>
+        <v>178</v>
       </c>
       <c r="F215" t="s">
         <v>220</v>
@@ -14823,22 +14850,22 @@
     </row>
     <row r="216" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B216" s="2">
-        <v>46310.508009259262</v>
+        <v>46323.659814814811</v>
       </c>
       <c r="C216" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D216" t="s">
         <v>248</v>
       </c>
       <c r="E216" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="F216" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G216" t="s">
         <v>36</v>
@@ -14880,22 +14907,22 @@
     </row>
     <row r="217" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B217" s="2">
-        <v>46310.508009259262</v>
+        <v>46323.659814814811</v>
       </c>
       <c r="C217" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D217" t="s">
         <v>248</v>
       </c>
       <c r="E217" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="F217" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="G217" t="s">
         <v>29</v>
@@ -14937,13 +14964,13 @@
     </row>
     <row r="218" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B218" s="2">
         <v>46311.629664351851</v>
       </c>
       <c r="C218" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D218" t="s">
         <v>26</v>
@@ -14952,7 +14979,7 @@
         <v>65</v>
       </c>
       <c r="F218" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="G218" t="s">
         <v>36</v>
@@ -14994,13 +15021,13 @@
     </row>
     <row r="219" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B219" s="2">
         <v>46311.629664351851</v>
       </c>
       <c r="C219" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D219" t="s">
         <v>26</v>
@@ -15009,7 +15036,7 @@
         <v>65</v>
       </c>
       <c r="F219" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="G219" t="s">
         <v>36</v>
@@ -15051,13 +15078,13 @@
     </row>
     <row r="220" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B220" s="2">
         <v>46311.629664351851</v>
       </c>
       <c r="C220" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D220" t="s">
         <v>26</v>
@@ -15066,7 +15093,7 @@
         <v>65</v>
       </c>
       <c r="F220" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="G220" t="s">
         <v>36</v>
@@ -15108,13 +15135,13 @@
     </row>
     <row r="221" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B221" s="2">
         <v>46311.629664351851</v>
       </c>
       <c r="C221" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D221" t="s">
         <v>26</v>
@@ -15123,7 +15150,7 @@
         <v>65</v>
       </c>
       <c r="F221" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="G221" t="s">
         <v>36</v>
@@ -15165,13 +15192,13 @@
     </row>
     <row r="222" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B222" s="2">
         <v>46311.679236111115</v>
       </c>
       <c r="C222" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D222" t="s">
         <v>243</v>
@@ -15180,7 +15207,7 @@
         <v>263</v>
       </c>
       <c r="F222" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G222" t="s">
         <v>269</v>
@@ -15222,13 +15249,13 @@
     </row>
     <row r="223" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B223" s="2">
         <v>46311.679236111115</v>
       </c>
       <c r="C223" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D223" t="s">
         <v>243</v>
@@ -15237,7 +15264,7 @@
         <v>263</v>
       </c>
       <c r="F223" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="G223" t="s">
         <v>269</v>
@@ -15279,22 +15306,22 @@
     </row>
     <row r="224" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B224" s="2">
-        <v>46311.673645833333</v>
+        <v>46323.660138888888</v>
       </c>
       <c r="C224" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D224" t="s">
         <v>70</v>
       </c>
       <c r="E224" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="F224" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="G224" t="s">
         <v>95</v>
@@ -15336,22 +15363,22 @@
     </row>
     <row r="225" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B225" s="2">
         <v>46311.685949074075</v>
       </c>
       <c r="C225" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D225" t="s">
         <v>243</v>
       </c>
       <c r="E225" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="F225" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="G225" t="s">
         <v>36</v>
@@ -15393,22 +15420,22 @@
     </row>
     <row r="226" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B226" s="2">
-        <v>46314.705381944441</v>
+        <v>46323.651331018518</v>
       </c>
       <c r="C226" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D226" t="s">
         <v>26</v>
       </c>
       <c r="E226" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F226" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G226" t="s">
         <v>36</v>
@@ -15450,22 +15477,22 @@
     </row>
     <row r="227" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B227" s="2">
-        <v>46314.705381944441</v>
+        <v>46323.651331018518</v>
       </c>
       <c r="C227" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D227" t="s">
         <v>26</v>
       </c>
       <c r="E227" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F227" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G227" t="s">
         <v>36</v>
@@ -15507,22 +15534,22 @@
     </row>
     <row r="228" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B228" s="2">
-        <v>46314.705381944441</v>
+        <v>46323.651331018518</v>
       </c>
       <c r="C228" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D228" t="s">
         <v>26</v>
       </c>
       <c r="E228" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F228" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G228" t="s">
         <v>36</v>
@@ -15564,22 +15591,22 @@
     </row>
     <row r="229" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B229" s="2">
-        <v>46314.705381944441</v>
+        <v>46323.651331018518</v>
       </c>
       <c r="C229" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D229" t="s">
         <v>26</v>
       </c>
       <c r="E229" t="s">
-        <v>497</v>
+        <v>50</v>
       </c>
       <c r="F229" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G229" t="s">
         <v>36</v>
@@ -15621,13 +15648,13 @@
     </row>
     <row r="230" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B230" s="2">
         <v>46314.559351851851</v>
       </c>
       <c r="C230" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D230" t="s">
         <v>26</v>
@@ -15636,7 +15663,7 @@
         <v>244</v>
       </c>
       <c r="F230" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="G230" t="s">
         <v>36</v>
@@ -15678,13 +15705,13 @@
     </row>
     <row r="231" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B231" s="2">
         <v>46314.559351851851</v>
       </c>
       <c r="C231" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D231" t="s">
         <v>26</v>
@@ -15693,7 +15720,7 @@
         <v>244</v>
       </c>
       <c r="F231" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="G231" t="s">
         <v>67</v>
@@ -15735,22 +15762,22 @@
     </row>
     <row r="232" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B232" s="2">
         <v>46315.62804398148</v>
       </c>
       <c r="C232" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D232" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E232" t="s">
         <v>65</v>
       </c>
       <c r="F232" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="G232" t="s">
         <v>73</v>
@@ -15792,22 +15819,22 @@
     </row>
     <row r="233" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B233" s="2">
         <v>46315.62804398148</v>
       </c>
       <c r="C233" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D233" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E233" t="s">
         <v>65</v>
       </c>
       <c r="F233" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G233" t="s">
         <v>73</v>
@@ -15849,22 +15876,22 @@
     </row>
     <row r="234" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B234" s="2">
         <v>46315.62804398148</v>
       </c>
       <c r="C234" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D234" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E234" t="s">
         <v>65</v>
       </c>
       <c r="F234" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G234" t="s">
         <v>73</v>
@@ -15906,22 +15933,22 @@
     </row>
     <row r="235" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B235" s="2">
         <v>46315.62804398148</v>
       </c>
       <c r="C235" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D235" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E235" t="s">
         <v>65</v>
       </c>
       <c r="F235" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G235" t="s">
         <v>36</v>
@@ -15963,22 +15990,22 @@
     </row>
     <row r="236" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B236" s="2">
         <v>46315.62804398148</v>
       </c>
       <c r="C236" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D236" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E236" t="s">
         <v>65</v>
       </c>
       <c r="F236" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="G236" t="s">
         <v>36</v>
@@ -16020,22 +16047,22 @@
     </row>
     <row r="237" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B237" s="2">
         <v>46315.710856481484</v>
       </c>
       <c r="C237" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D237" t="s">
         <v>26</v>
       </c>
       <c r="E237" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F237" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="G237" t="s">
         <v>29</v>
@@ -16077,13 +16104,13 @@
     </row>
     <row r="238" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B238" s="2">
         <v>46315.718298611115</v>
       </c>
       <c r="C238" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D238" t="s">
         <v>26</v>
@@ -16092,7 +16119,7 @@
         <v>158</v>
       </c>
       <c r="F238" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="G238" t="s">
         <v>95</v>
@@ -16134,13 +16161,13 @@
     </row>
     <row r="239" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B239" s="2">
         <v>46317.650775462964</v>
       </c>
       <c r="C239" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D239" t="s">
         <v>26</v>
@@ -16149,7 +16176,7 @@
         <v>244</v>
       </c>
       <c r="F239" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="G239" t="s">
         <v>36</v>
@@ -16191,13 +16218,13 @@
     </row>
     <row r="240" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B240" s="2">
         <v>46317.650775462964</v>
       </c>
       <c r="C240" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D240" t="s">
         <v>26</v>
@@ -16206,7 +16233,7 @@
         <v>244</v>
       </c>
       <c r="F240" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="G240" t="s">
         <v>67</v>
@@ -16248,13 +16275,13 @@
     </row>
     <row r="241" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B241" s="2">
         <v>46317.650775462964</v>
       </c>
       <c r="C241" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D241" t="s">
         <v>26</v>
@@ -16263,10 +16290,10 @@
         <v>244</v>
       </c>
       <c r="F241" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="G241" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H241">
         <v>150000</v>
@@ -16305,13 +16332,13 @@
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B242" s="2">
         <v>46317.650925925926</v>
       </c>
       <c r="C242" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D242" t="s">
         <v>26</v>
@@ -16320,7 +16347,7 @@
         <v>244</v>
       </c>
       <c r="F242" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="G242" t="s">
         <v>36</v>
@@ -16362,13 +16389,13 @@
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B243" s="2">
         <v>46317.650925925926</v>
       </c>
       <c r="C243" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D243" t="s">
         <v>26</v>
@@ -16377,7 +16404,7 @@
         <v>244</v>
       </c>
       <c r="F243" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="G243" t="s">
         <v>67</v>
@@ -16419,13 +16446,13 @@
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B244" s="2">
         <v>46317.650925925926</v>
       </c>
       <c r="C244" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D244" t="s">
         <v>26</v>
@@ -16434,10 +16461,10 @@
         <v>244</v>
       </c>
       <c r="F244" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="G244" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H244">
         <v>150000</v>
@@ -16476,22 +16503,22 @@
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B245" s="2">
         <v>46317.409386574072</v>
       </c>
       <c r="C245" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D245" t="s">
         <v>258</v>
       </c>
       <c r="E245" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F245" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="G245" t="s">
         <v>36</v>
@@ -16533,22 +16560,22 @@
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B246" s="2">
         <v>46317.409386574072</v>
       </c>
       <c r="C246" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D246" t="s">
         <v>258</v>
       </c>
       <c r="E246" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F246" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="G246" t="s">
         <v>36</v>
@@ -16590,22 +16617,22 @@
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B247" s="2">
         <v>46317.409386574072</v>
       </c>
       <c r="C247" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D247" t="s">
         <v>258</v>
       </c>
       <c r="E247" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F247" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="G247" t="s">
         <v>36</v>
@@ -16647,22 +16674,22 @@
     </row>
     <row r="248" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B248" s="2">
         <v>46317.409386574072</v>
       </c>
       <c r="C248" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D248" t="s">
         <v>258</v>
       </c>
       <c r="E248" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F248" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="G248" t="s">
         <v>36</v>
@@ -16704,22 +16731,22 @@
     </row>
     <row r="249" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B249" s="2">
         <v>46318.614328703705</v>
       </c>
       <c r="C249" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D249" t="s">
         <v>258</v>
       </c>
       <c r="E249" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F249" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="G249" t="s">
         <v>73</v>
@@ -16761,13 +16788,13 @@
     </row>
     <row r="250" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B250" s="2">
         <v>46318.665462962963</v>
       </c>
       <c r="C250" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D250" t="s">
         <v>26</v>
@@ -16776,7 +16803,7 @@
         <v>27</v>
       </c>
       <c r="F250" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G250" t="s">
         <v>52</v>
@@ -16818,13 +16845,13 @@
     </row>
     <row r="251" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B251" s="2">
         <v>46318.665462962963</v>
       </c>
       <c r="C251" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D251" t="s">
         <v>26</v>
@@ -16833,7 +16860,7 @@
         <v>27</v>
       </c>
       <c r="F251" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="G251" t="s">
         <v>52</v>
@@ -16875,13 +16902,13 @@
     </row>
     <row r="252" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B252" s="2">
         <v>46318.665462962963</v>
       </c>
       <c r="C252" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D252" t="s">
         <v>26</v>
@@ -16890,7 +16917,7 @@
         <v>27</v>
       </c>
       <c r="F252" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="G252" t="s">
         <v>52</v>
@@ -16932,13 +16959,13 @@
     </row>
     <row r="253" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B253" s="2">
         <v>46318.646168981482</v>
       </c>
       <c r="C253" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D253" t="s">
         <v>243</v>
@@ -16947,7 +16974,7 @@
         <v>244</v>
       </c>
       <c r="F253" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G253" t="s">
         <v>201</v>
@@ -16989,13 +17016,13 @@
     </row>
     <row r="254" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B254" s="2">
         <v>46318.646168981482</v>
       </c>
       <c r="C254" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D254" t="s">
         <v>243</v>
@@ -17004,7 +17031,7 @@
         <v>244</v>
       </c>
       <c r="F254" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="G254" t="s">
         <v>36</v>
@@ -17046,13 +17073,13 @@
     </row>
     <row r="255" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B255" s="2">
-        <v>46318.702164351853</v>
+        <v>46321.403553240743</v>
       </c>
       <c r="C255" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D255" t="s">
         <v>26</v>
@@ -17061,55 +17088,55 @@
         <v>27</v>
       </c>
       <c r="F255" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="G255" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="H255">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I255" s="3">
-        <v>139.27000000000001</v>
+        <v>767.09</v>
       </c>
       <c r="J255" s="3">
-        <v>2785.4</v>
+        <v>3835.45</v>
       </c>
       <c r="K255">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L255" s="3">
-        <v>0</v>
+        <v>540.62</v>
       </c>
       <c r="M255" s="3">
-        <v>0</v>
+        <v>5406.2</v>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O255" s="3">
-        <v>0</v>
+        <v>458.18</v>
       </c>
       <c r="P255" s="3">
-        <v>0</v>
+        <v>6872.7</v>
       </c>
       <c r="Q255" s="1">
         <v>0</v>
       </c>
       <c r="R255" s="1">
-        <v>2785.4</v>
+        <v>5371.45</v>
       </c>
       <c r="V255" s="2"/>
     </row>
     <row r="256" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B256" s="2">
-        <v>46318.702164351853</v>
+        <v>46321.403553240743</v>
       </c>
       <c r="C256" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D256" t="s">
         <v>26</v>
@@ -17118,55 +17145,55 @@
         <v>27</v>
       </c>
       <c r="F256" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="G256" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="H256">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I256" s="3">
-        <v>160.69999999999999</v>
+        <v>767.34</v>
       </c>
       <c r="J256" s="3">
-        <v>3214</v>
+        <v>3836.7</v>
       </c>
       <c r="K256">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L256" s="3">
-        <v>0</v>
+        <v>540.17999999999995</v>
       </c>
       <c r="M256" s="3">
-        <v>0</v>
+        <v>5401.8</v>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O256" s="3">
-        <v>0</v>
+        <v>457.54</v>
       </c>
       <c r="P256" s="3">
-        <v>0</v>
+        <v>6863.1</v>
       </c>
       <c r="Q256" s="1">
         <v>0</v>
       </c>
       <c r="R256" s="1">
-        <v>2785.4</v>
+        <v>5371.45</v>
       </c>
       <c r="V256" s="2"/>
     </row>
     <row r="257" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B257" s="2">
-        <v>46318.702164351853</v>
+        <v>46321.403553240743</v>
       </c>
       <c r="C257" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D257" t="s">
         <v>26</v>
@@ -17175,52 +17202,52 @@
         <v>27</v>
       </c>
       <c r="F257" t="s">
-        <v>588</v>
+        <v>478</v>
       </c>
       <c r="G257" t="s">
-        <v>239</v>
+        <v>73</v>
       </c>
       <c r="H257">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I257" s="3">
-        <v>160.69</v>
+        <v>121.55</v>
       </c>
       <c r="J257" s="3">
-        <v>3213.8</v>
+        <v>3038.75</v>
       </c>
       <c r="K257">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L257" s="3">
-        <v>0</v>
+        <v>113.6</v>
       </c>
       <c r="M257" s="3">
-        <v>0</v>
+        <v>3976</v>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O257" s="3">
-        <v>0</v>
+        <v>109.31</v>
       </c>
       <c r="P257" s="3">
-        <v>0</v>
+        <v>5465.5</v>
       </c>
       <c r="Q257" s="1">
         <v>0</v>
       </c>
       <c r="R257" s="1">
-        <v>2785.4</v>
+        <v>4160.083333333333</v>
       </c>
       <c r="V257" s="2"/>
     </row>
     <row r="258" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B258" s="2">
-        <v>46322.65556712963</v>
+        <v>46321.40457175926</v>
       </c>
       <c r="C258" t="s">
         <v>587</v>
@@ -17232,52 +17259,52 @@
         <v>27</v>
       </c>
       <c r="F258" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G258" t="s">
         <v>52</v>
       </c>
       <c r="H258">
+        <v>10</v>
+      </c>
+      <c r="I258" s="3">
+        <v>407.73</v>
+      </c>
+      <c r="J258" s="3">
+        <v>4077.3</v>
+      </c>
+      <c r="K258">
         <v>20</v>
       </c>
-      <c r="I258" s="3">
-        <v>268.89</v>
-      </c>
-      <c r="J258" s="3">
-        <v>5377.8</v>
-      </c>
-      <c r="K258">
-        <v>0</v>
-      </c>
       <c r="L258" s="3">
-        <v>0</v>
+        <v>328.97</v>
       </c>
       <c r="M258" s="3">
-        <v>0</v>
+        <v>6579.4</v>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O258" s="3">
-        <v>0</v>
+        <v>293.49</v>
       </c>
       <c r="P258" s="3">
-        <v>0</v>
+        <v>8804.7000000000007</v>
       </c>
       <c r="Q258" s="1">
         <v>0</v>
       </c>
       <c r="R258" s="1">
-        <v>5377.8</v>
+        <v>6487.1333333333341</v>
       </c>
       <c r="V258" s="2"/>
     </row>
     <row r="259" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B259" s="2">
-        <v>46322.65556712963</v>
+        <v>46321.40457175926</v>
       </c>
       <c r="C259" t="s">
         <v>587</v>
@@ -17289,43 +17316,43 @@
         <v>27</v>
       </c>
       <c r="F259" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="G259" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="H259">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I259" s="3">
-        <v>195.81</v>
+        <v>121.55</v>
       </c>
       <c r="J259" s="3">
-        <v>3916.2</v>
+        <v>3038.75</v>
       </c>
       <c r="K259">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L259" s="3">
-        <v>0</v>
+        <v>113.6</v>
       </c>
       <c r="M259" s="3">
-        <v>0</v>
+        <v>3976</v>
       </c>
       <c r="N259">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O259" s="3">
-        <v>0</v>
+        <v>109.31</v>
       </c>
       <c r="P259" s="3">
-        <v>0</v>
+        <v>5465.5</v>
       </c>
       <c r="Q259" s="1">
         <v>0</v>
       </c>
       <c r="R259" s="1">
-        <v>3916.2</v>
+        <v>4160.083333333333</v>
       </c>
       <c r="V259" s="2"/>
     </row>
@@ -17334,31 +17361,31 @@
         <v>589</v>
       </c>
       <c r="B260" s="2">
-        <v>46322.65556712963</v>
+        <v>46323.647199074076</v>
       </c>
       <c r="C260" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D260" t="s">
         <v>26</v>
       </c>
       <c r="E260" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="F260" t="s">
-        <v>592</v>
+        <v>343</v>
       </c>
       <c r="G260" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H260">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="I260" s="3">
-        <v>155.62</v>
+        <v>95.9</v>
       </c>
       <c r="J260" s="3">
-        <v>3112.4</v>
+        <v>19180</v>
       </c>
       <c r="K260">
         <v>0</v>
@@ -17382,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="R260" s="1">
-        <v>3112.4</v>
+        <v>19180</v>
       </c>
       <c r="V260" s="2"/>
     </row>
@@ -17391,31 +17418,31 @@
         <v>589</v>
       </c>
       <c r="B261" s="2">
-        <v>46322.65556712963</v>
+        <v>46323.647199074076</v>
       </c>
       <c r="C261" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D261" t="s">
         <v>26</v>
       </c>
       <c r="E261" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="F261" t="s">
-        <v>592</v>
+        <v>343</v>
       </c>
       <c r="G261" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="H261">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="I261" s="3">
-        <v>183.2</v>
+        <v>107.61</v>
       </c>
       <c r="J261" s="3">
-        <v>3664</v>
+        <v>21522</v>
       </c>
       <c r="K261">
         <v>0</v>
@@ -17439,64 +17466,64 @@
         <v>0</v>
       </c>
       <c r="R261" s="1">
-        <v>3112.4</v>
+        <v>19180</v>
       </c>
       <c r="V261" s="2"/>
     </row>
     <row r="262" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B262" s="2">
-        <v>46322.65556712963</v>
+        <v>46322.433032407411</v>
       </c>
       <c r="C262" t="s">
-        <v>587</v>
+        <v>482</v>
       </c>
       <c r="D262" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="E262" t="s">
-        <v>27</v>
+        <v>592</v>
       </c>
       <c r="F262" t="s">
         <v>593</v>
       </c>
       <c r="G262" t="s">
-        <v>239</v>
+        <v>36</v>
       </c>
       <c r="H262">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I262" s="3">
-        <v>190.39</v>
+        <v>72.19</v>
       </c>
       <c r="J262" s="3">
-        <v>3807.8</v>
+        <v>2887.6</v>
       </c>
       <c r="K262">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L262" s="3">
-        <v>0</v>
+        <v>59.72</v>
       </c>
       <c r="M262" s="3">
-        <v>0</v>
+        <v>3284.6</v>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O262" s="3">
-        <v>0</v>
+        <v>50.83</v>
       </c>
       <c r="P262" s="3">
-        <v>0</v>
+        <v>3812.25</v>
       </c>
       <c r="Q262" s="1">
         <v>0</v>
       </c>
       <c r="R262" s="1">
-        <v>3807.8</v>
+        <v>3328.15</v>
       </c>
       <c r="V262" s="2"/>
     </row>
@@ -17505,7 +17532,7 @@
         <v>594</v>
       </c>
       <c r="B263" s="2">
-        <v>46321.403553240743</v>
+        <v>46322.652777777781</v>
       </c>
       <c r="C263" t="s">
         <v>595</v>
@@ -17520,106 +17547,106 @@
         <v>596</v>
       </c>
       <c r="G263" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="H263">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="I263" s="3">
-        <v>767.09</v>
+        <v>105.34</v>
       </c>
       <c r="J263" s="3">
-        <v>3835.45</v>
+        <v>5267</v>
       </c>
       <c r="K263">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L263" s="3">
-        <v>540.62</v>
+        <v>0</v>
       </c>
       <c r="M263" s="3">
-        <v>5406.2</v>
+        <v>0</v>
       </c>
       <c r="N263">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O263" s="3">
-        <v>458.18</v>
+        <v>0</v>
       </c>
       <c r="P263" s="3">
-        <v>6872.7</v>
+        <v>0</v>
       </c>
       <c r="Q263" s="1">
         <v>0</v>
       </c>
       <c r="R263" s="1">
-        <v>5371.45</v>
+        <v>5267</v>
       </c>
       <c r="V263" s="2"/>
     </row>
     <row r="264" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B264" s="2">
-        <v>46321.403553240743</v>
+        <v>46322.660601851851</v>
       </c>
       <c r="C264" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D264" t="s">
         <v>26</v>
       </c>
       <c r="E264" t="s">
-        <v>27</v>
+        <v>244</v>
       </c>
       <c r="F264" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="G264" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="H264">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I264" s="3">
-        <v>767.34</v>
+        <v>31.57</v>
       </c>
       <c r="J264" s="3">
-        <v>3836.7</v>
+        <v>3157</v>
       </c>
       <c r="K264">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="L264" s="3">
-        <v>540.17999999999995</v>
+        <v>28.95</v>
       </c>
       <c r="M264" s="3">
-        <v>5401.8</v>
+        <v>4053</v>
       </c>
       <c r="N264">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="O264" s="3">
-        <v>457.54</v>
+        <v>27.83</v>
       </c>
       <c r="P264" s="3">
-        <v>6863.1</v>
+        <v>4480.63</v>
       </c>
       <c r="Q264" s="1">
         <v>0</v>
       </c>
       <c r="R264" s="1">
-        <v>5371.45</v>
+        <v>3896.876666666667</v>
       </c>
       <c r="V264" s="2"/>
     </row>
     <row r="265" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B265" s="2">
-        <v>46321.403553240743</v>
+        <v>46323.367650462962</v>
       </c>
       <c r="C265" t="s">
         <v>595</v>
@@ -17631,55 +17658,55 @@
         <v>27</v>
       </c>
       <c r="F265" t="s">
-        <v>478</v>
+        <v>601</v>
       </c>
       <c r="G265" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="H265">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I265" s="3">
-        <v>121.55</v>
+        <v>139.27000000000001</v>
       </c>
       <c r="J265" s="3">
-        <v>3038.75</v>
+        <v>2785.4</v>
       </c>
       <c r="K265">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L265" s="3">
-        <v>113.6</v>
+        <v>104.3</v>
       </c>
       <c r="M265" s="3">
-        <v>3976</v>
+        <v>3129</v>
       </c>
       <c r="N265">
         <v>50</v>
       </c>
       <c r="O265" s="3">
-        <v>109.31</v>
+        <v>77.48</v>
       </c>
       <c r="P265" s="3">
-        <v>5465.5</v>
+        <v>3874</v>
       </c>
       <c r="Q265" s="1">
         <v>0</v>
       </c>
       <c r="R265" s="1">
-        <v>4160.083333333333</v>
+        <v>3262.7999999999997</v>
       </c>
       <c r="V265" s="2"/>
     </row>
     <row r="266" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B266" s="2">
-        <v>46321.40457175926</v>
+        <v>46323.367650462962</v>
       </c>
       <c r="C266" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D266" t="s">
         <v>26</v>
@@ -17688,55 +17715,55 @@
         <v>27</v>
       </c>
       <c r="F266" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="G266" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="H266">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I266" s="3">
-        <v>407.73</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="J266" s="3">
-        <v>4077.3</v>
+        <v>3214</v>
       </c>
       <c r="K266">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L266" s="3">
-        <v>328.97</v>
+        <v>120.82</v>
       </c>
       <c r="M266" s="3">
-        <v>6579.4</v>
+        <v>3624.6</v>
       </c>
       <c r="N266">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O266" s="3">
-        <v>293.49</v>
+        <v>90.26</v>
       </c>
       <c r="P266" s="3">
-        <v>8804.7000000000007</v>
+        <v>4513</v>
       </c>
       <c r="Q266" s="1">
         <v>0</v>
       </c>
       <c r="R266" s="1">
-        <v>6487.1333333333341</v>
+        <v>3262.7999999999997</v>
       </c>
       <c r="V266" s="2"/>
     </row>
     <row r="267" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B267" s="2">
-        <v>46321.40457175926</v>
+        <v>46323.367650462962</v>
       </c>
       <c r="C267" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D267" t="s">
         <v>26</v>
@@ -17745,43 +17772,43 @@
         <v>27</v>
       </c>
       <c r="F267" t="s">
-        <v>559</v>
+        <v>601</v>
       </c>
       <c r="G267" t="s">
-        <v>73</v>
+        <v>239</v>
       </c>
       <c r="H267">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I267" s="3">
-        <v>121.55</v>
+        <v>160.69</v>
       </c>
       <c r="J267" s="3">
-        <v>3038.75</v>
+        <v>3213.8</v>
       </c>
       <c r="K267">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L267" s="3">
-        <v>113.6</v>
+        <v>120.72</v>
       </c>
       <c r="M267" s="3">
-        <v>3976</v>
+        <v>3621.6</v>
       </c>
       <c r="N267">
         <v>50</v>
       </c>
       <c r="O267" s="3">
-        <v>109.31</v>
+        <v>90.07</v>
       </c>
       <c r="P267" s="3">
-        <v>5465.5</v>
+        <v>4503.5</v>
       </c>
       <c r="Q267" s="1">
         <v>0</v>
       </c>
       <c r="R267" s="1">
-        <v>4160.083333333333</v>
+        <v>3262.7999999999997</v>
       </c>
       <c r="V267" s="2"/>
     </row>
@@ -17790,295 +17817,295 @@
         <v>600</v>
       </c>
       <c r="B268" s="2">
-        <v>46322.720046296294</v>
+        <v>46323.447129629632</v>
       </c>
       <c r="C268" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D268" t="s">
         <v>26</v>
       </c>
       <c r="E268" t="s">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="F268" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G268" t="s">
-        <v>98</v>
+        <v>604</v>
       </c>
       <c r="H268">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="I268" s="3">
-        <v>169.52</v>
+        <v>22.74</v>
       </c>
       <c r="J268" s="3">
-        <v>2542.8000000000002</v>
+        <v>2387.6999999999998</v>
       </c>
       <c r="K268">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L268" s="3">
-        <v>146.38999999999999</v>
+        <v>0</v>
       </c>
       <c r="M268" s="3">
-        <v>2927.8</v>
+        <v>0</v>
       </c>
       <c r="N268">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O268" s="3">
-        <v>123.01</v>
+        <v>0</v>
       </c>
       <c r="P268" s="3">
-        <v>3690.3</v>
+        <v>0</v>
       </c>
       <c r="Q268" s="1">
         <v>0</v>
       </c>
       <c r="R268" s="1">
-        <v>3053.6333333333337</v>
+        <v>2387.6999999999998</v>
       </c>
       <c r="V268" s="2"/>
     </row>
     <row r="269" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="B269" s="2">
-        <v>46322.720046296294</v>
+        <v>46323.371018518519</v>
       </c>
       <c r="C269" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="D269" t="s">
         <v>26</v>
       </c>
       <c r="E269" t="s">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="F269" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="G269" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="H269">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I269" s="3">
-        <v>404.07</v>
+        <v>268.89</v>
       </c>
       <c r="J269" s="3">
-        <v>6061.05</v>
+        <v>5377.8</v>
       </c>
       <c r="K269">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L269" s="3">
-        <v>318.43</v>
+        <v>236.76</v>
       </c>
       <c r="M269" s="3">
-        <v>6368.6</v>
+        <v>7102.8</v>
       </c>
       <c r="N269">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O269" s="3">
-        <v>235.34</v>
+        <v>209.24</v>
       </c>
       <c r="P269" s="3">
-        <v>7060.2</v>
+        <v>10462</v>
       </c>
       <c r="Q269" s="1">
         <v>0</v>
       </c>
       <c r="R269" s="1">
-        <v>3053.6333333333337</v>
+        <v>7647.5333333333328</v>
       </c>
       <c r="V269" s="2"/>
     </row>
     <row r="270" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B270" s="2">
-        <v>46322.382893518516</v>
+        <v>46323.371018518519</v>
       </c>
       <c r="C270" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D270" t="s">
         <v>26</v>
       </c>
       <c r="E270" t="s">
-        <v>605</v>
+        <v>27</v>
       </c>
       <c r="F270" t="s">
-        <v>343</v>
+        <v>596</v>
       </c>
       <c r="G270" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="H270">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="I270" s="3">
-        <v>95.9</v>
+        <v>195.81</v>
       </c>
       <c r="J270" s="3">
-        <v>19180</v>
+        <v>3916.2</v>
       </c>
       <c r="K270">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L270" s="3">
-        <v>0</v>
+        <v>153.69</v>
       </c>
       <c r="M270" s="3">
-        <v>0</v>
+        <v>4610.7</v>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O270" s="3">
-        <v>0</v>
+        <v>125.88</v>
       </c>
       <c r="P270" s="3">
-        <v>0</v>
+        <v>6294</v>
       </c>
       <c r="Q270" s="1">
         <v>0</v>
       </c>
       <c r="R270" s="1">
-        <v>19180</v>
+        <v>4940.3</v>
       </c>
       <c r="V270" s="2"/>
     </row>
     <row r="271" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B271" s="2">
-        <v>46322.382893518516</v>
+        <v>46323.371018518519</v>
       </c>
       <c r="C271" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D271" t="s">
         <v>26</v>
       </c>
       <c r="E271" t="s">
-        <v>605</v>
+        <v>27</v>
       </c>
       <c r="F271" t="s">
-        <v>343</v>
+        <v>607</v>
       </c>
       <c r="G271" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H271">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="I271" s="3">
-        <v>107.61</v>
+        <v>155.62</v>
       </c>
       <c r="J271" s="3">
-        <v>21522</v>
+        <v>3112.4</v>
       </c>
       <c r="K271">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L271" s="3">
-        <v>0</v>
+        <v>123.1</v>
       </c>
       <c r="M271" s="3">
-        <v>0</v>
+        <v>3693</v>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O271" s="3">
-        <v>0</v>
+        <v>102.83</v>
       </c>
       <c r="P271" s="3">
-        <v>0</v>
+        <v>5141.5</v>
       </c>
       <c r="Q271" s="1">
         <v>0</v>
       </c>
       <c r="R271" s="1">
-        <v>19180</v>
+        <v>3982.2999999999997</v>
       </c>
       <c r="V271" s="2"/>
     </row>
     <row r="272" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B272" s="2">
-        <v>46322.433032407411</v>
+        <v>46323.371018518519</v>
       </c>
       <c r="C272" t="s">
-        <v>482</v>
+        <v>595</v>
       </c>
       <c r="D272" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="E272" t="s">
-        <v>469</v>
+        <v>27</v>
       </c>
       <c r="F272" t="s">
         <v>607</v>
       </c>
       <c r="G272" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="H272">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I272" s="3">
-        <v>72.19</v>
+        <v>183.2</v>
       </c>
       <c r="J272" s="3">
-        <v>2887.6</v>
+        <v>3664</v>
       </c>
       <c r="K272">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L272" s="3">
-        <v>59.72</v>
+        <v>145.9</v>
       </c>
       <c r="M272" s="3">
-        <v>3284.6</v>
+        <v>4377</v>
       </c>
       <c r="N272">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O272" s="3">
-        <v>50.83</v>
+        <v>123.04</v>
       </c>
       <c r="P272" s="3">
-        <v>3812.25</v>
+        <v>6152</v>
       </c>
       <c r="Q272" s="1">
         <v>0</v>
       </c>
       <c r="R272" s="1">
-        <v>3328.15</v>
+        <v>3982.2999999999997</v>
       </c>
       <c r="V272" s="2"/>
     </row>
     <row r="273" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B273" s="2">
-        <v>46322.652777777781</v>
+        <v>46323.371018518519</v>
       </c>
       <c r="C273" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="D273" t="s">
         <v>26</v>
@@ -18087,43 +18114,43 @@
         <v>27</v>
       </c>
       <c r="F273" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="G273" t="s">
-        <v>73</v>
+        <v>239</v>
       </c>
       <c r="H273">
+        <v>20</v>
+      </c>
+      <c r="I273" s="3">
+        <v>190.39</v>
+      </c>
+      <c r="J273" s="3">
+        <v>3807.8</v>
+      </c>
+      <c r="K273">
+        <v>30</v>
+      </c>
+      <c r="L273" s="3">
+        <v>151.44999999999999</v>
+      </c>
+      <c r="M273" s="3">
+        <v>4543.5</v>
+      </c>
+      <c r="N273">
         <v>50</v>
       </c>
-      <c r="I273" s="3">
-        <v>105.34</v>
-      </c>
-      <c r="J273" s="3">
-        <v>5267</v>
-      </c>
-      <c r="K273">
-        <v>0</v>
-      </c>
-      <c r="L273" s="3">
-        <v>0</v>
-      </c>
-      <c r="M273" s="3">
-        <v>0</v>
-      </c>
-      <c r="N273">
-        <v>0</v>
-      </c>
       <c r="O273" s="3">
-        <v>0</v>
+        <v>127.52</v>
       </c>
       <c r="P273" s="3">
-        <v>0</v>
+        <v>6376</v>
       </c>
       <c r="Q273" s="1">
         <v>0</v>
       </c>
       <c r="R273" s="1">
-        <v>5267</v>
+        <v>4909.0999999999995</v>
       </c>
       <c r="V273" s="2"/>
     </row>
@@ -18132,114 +18159,339 @@
         <v>609</v>
       </c>
       <c r="B274" s="2">
-        <v>46322.660601851851</v>
+        <v>46323.468159722222</v>
       </c>
       <c r="C274" t="s">
         <v>610</v>
       </c>
       <c r="D274" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="E274" t="s">
-        <v>244</v>
+        <v>417</v>
       </c>
       <c r="F274" t="s">
         <v>611</v>
       </c>
       <c r="G274" t="s">
+        <v>115</v>
+      </c>
+      <c r="H274">
+        <v>25</v>
+      </c>
+      <c r="I274" s="3">
+        <v>128.01</v>
+      </c>
+      <c r="J274" s="3">
+        <v>3200.25</v>
+      </c>
+      <c r="K274">
+        <v>35</v>
+      </c>
+      <c r="L274" s="3">
+        <v>105.92</v>
+      </c>
+      <c r="M274" s="3">
+        <v>3707.2</v>
+      </c>
+      <c r="N274">
+        <v>50</v>
+      </c>
+      <c r="O274" s="3">
+        <v>93.24</v>
+      </c>
+      <c r="P274" s="3">
+        <v>4662</v>
+      </c>
+      <c r="Q274" s="1">
+        <v>0</v>
+      </c>
+      <c r="R274" s="1">
+        <v>3856.4833333333336</v>
+      </c>
+      <c r="V274" s="2"/>
+    </row>
+    <row r="275" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>612</v>
+      </c>
+      <c r="B275" s="2">
+        <v>46323.62091435185</v>
+      </c>
+      <c r="C275" t="s">
+        <v>356</v>
+      </c>
+      <c r="D275" t="s">
+        <v>26</v>
+      </c>
+      <c r="E275" t="s">
+        <v>45</v>
+      </c>
+      <c r="F275" t="s">
+        <v>613</v>
+      </c>
+      <c r="G275" t="s">
+        <v>239</v>
+      </c>
+      <c r="H275">
+        <v>115</v>
+      </c>
+      <c r="I275" s="3">
+        <v>21.76</v>
+      </c>
+      <c r="J275" s="3">
+        <v>2502.4</v>
+      </c>
+      <c r="K275">
+        <v>155</v>
+      </c>
+      <c r="L275" s="3">
+        <v>20.9</v>
+      </c>
+      <c r="M275" s="3">
+        <v>3239.5</v>
+      </c>
+      <c r="N275">
+        <v>210</v>
+      </c>
+      <c r="O275" s="3">
+        <v>19.2</v>
+      </c>
+      <c r="P275" s="3">
+        <v>4032</v>
+      </c>
+      <c r="Q275" s="1">
+        <v>0</v>
+      </c>
+      <c r="R275" s="1">
+        <v>3257.9666666666667</v>
+      </c>
+      <c r="V275" s="2"/>
+    </row>
+    <row r="276" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>614</v>
+      </c>
+      <c r="B276" s="2">
+        <v>46323.596215277779</v>
+      </c>
+      <c r="C276" t="s">
+        <v>615</v>
+      </c>
+      <c r="D276" t="s">
+        <v>26</v>
+      </c>
+      <c r="E276" t="s">
+        <v>174</v>
+      </c>
+      <c r="F276" t="s">
+        <v>616</v>
+      </c>
+      <c r="G276" t="s">
         <v>98</v>
       </c>
-      <c r="H274">
-        <v>100</v>
-      </c>
-      <c r="I274" s="3">
-        <v>31.57</v>
-      </c>
-      <c r="J274" s="3">
-        <v>3157</v>
-      </c>
-      <c r="K274">
-        <v>140</v>
-      </c>
-      <c r="L274" s="3">
-        <v>28.95</v>
-      </c>
-      <c r="M274" s="3">
-        <v>4053</v>
-      </c>
-      <c r="N274">
-        <v>161</v>
-      </c>
-      <c r="O274" s="3">
-        <v>27.83</v>
-      </c>
-      <c r="P274" s="3">
-        <v>4480.63</v>
-      </c>
-      <c r="Q274" s="1">
-        <v>0</v>
-      </c>
-      <c r="R274" s="1">
-        <v>3896.876666666667</v>
-      </c>
-      <c r="V274" s="2"/>
-    </row>
-    <row r="275" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B275" s="2"/>
-      <c r="I275" s="1"/>
-      <c r="J275" s="1"/>
-      <c r="L275" s="1"/>
-      <c r="M275" s="1"/>
-      <c r="O275" s="1"/>
-      <c r="P275" s="1"/>
-      <c r="Q275" s="1"/>
-      <c r="R275" s="1"/>
-      <c r="V275" s="2"/>
-    </row>
-    <row r="276" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B276" s="2"/>
-      <c r="I276" s="1"/>
-      <c r="J276" s="1"/>
-      <c r="L276" s="1"/>
-      <c r="M276" s="1"/>
-      <c r="O276" s="1"/>
-      <c r="P276" s="1"/>
-      <c r="Q276" s="1"/>
-      <c r="R276" s="1"/>
+      <c r="H276">
+        <v>15</v>
+      </c>
+      <c r="I276" s="3">
+        <v>169.52</v>
+      </c>
+      <c r="J276" s="3">
+        <v>2542.8000000000002</v>
+      </c>
+      <c r="K276">
+        <v>20</v>
+      </c>
+      <c r="L276" s="3">
+        <v>146.38999999999999</v>
+      </c>
+      <c r="M276" s="3">
+        <v>2927.8</v>
+      </c>
+      <c r="N276">
+        <v>30</v>
+      </c>
+      <c r="O276" s="3">
+        <v>123.01</v>
+      </c>
+      <c r="P276" s="3">
+        <v>3690.3</v>
+      </c>
+      <c r="Q276" s="1">
+        <v>0</v>
+      </c>
+      <c r="R276" s="1">
+        <v>3053.6333333333337</v>
+      </c>
       <c r="V276" s="2"/>
     </row>
     <row r="277" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B277" s="4"/>
-      <c r="I277" s="1"/>
-      <c r="J277" s="1"/>
-      <c r="L277" s="1"/>
-      <c r="M277" s="1"/>
-      <c r="O277" s="1"/>
-      <c r="P277" s="1"/>
-      <c r="Q277" s="1"/>
-      <c r="R277" s="1"/>
+      <c r="A277" t="s">
+        <v>614</v>
+      </c>
+      <c r="B277" s="4">
+        <v>46323.596215277779</v>
+      </c>
+      <c r="C277" t="s">
+        <v>615</v>
+      </c>
+      <c r="D277" t="s">
+        <v>26</v>
+      </c>
+      <c r="E277" t="s">
+        <v>174</v>
+      </c>
+      <c r="F277" t="s">
+        <v>616</v>
+      </c>
+      <c r="G277" t="s">
+        <v>98</v>
+      </c>
+      <c r="H277">
+        <v>15</v>
+      </c>
+      <c r="I277" s="3">
+        <v>404.07</v>
+      </c>
+      <c r="J277" s="3">
+        <v>6061.05</v>
+      </c>
+      <c r="K277">
+        <v>20</v>
+      </c>
+      <c r="L277" s="3">
+        <v>318.43</v>
+      </c>
+      <c r="M277" s="3">
+        <v>6368.6</v>
+      </c>
+      <c r="N277">
+        <v>30</v>
+      </c>
+      <c r="O277" s="3">
+        <v>235.34</v>
+      </c>
+      <c r="P277" s="3">
+        <v>7060.2</v>
+      </c>
+      <c r="Q277" s="1">
+        <v>0</v>
+      </c>
+      <c r="R277" s="1">
+        <v>3053.6333333333337</v>
+      </c>
     </row>
     <row r="278" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B278" s="4"/>
-      <c r="I278" s="1"/>
-      <c r="J278" s="1"/>
-      <c r="L278" s="1"/>
-      <c r="M278" s="1"/>
-      <c r="O278" s="1"/>
-      <c r="P278" s="1"/>
-      <c r="Q278" s="1"/>
-      <c r="R278" s="1"/>
+      <c r="A278" t="s">
+        <v>614</v>
+      </c>
+      <c r="B278" s="4">
+        <v>46323.596215277779</v>
+      </c>
+      <c r="C278" t="s">
+        <v>615</v>
+      </c>
+      <c r="D278" t="s">
+        <v>26</v>
+      </c>
+      <c r="E278" t="s">
+        <v>174</v>
+      </c>
+      <c r="F278" t="s">
+        <v>616</v>
+      </c>
+      <c r="G278" t="s">
+        <v>98</v>
+      </c>
+      <c r="H278">
+        <v>15</v>
+      </c>
+      <c r="I278" s="3">
+        <v>430.13</v>
+      </c>
+      <c r="J278" s="3">
+        <v>6451.95</v>
+      </c>
+      <c r="K278">
+        <v>20</v>
+      </c>
+      <c r="L278" s="3">
+        <v>337.54</v>
+      </c>
+      <c r="M278" s="3">
+        <v>6750.8</v>
+      </c>
+      <c r="N278">
+        <v>30</v>
+      </c>
+      <c r="O278" s="3">
+        <v>247.82</v>
+      </c>
+      <c r="P278" s="3">
+        <v>7434.6</v>
+      </c>
+      <c r="Q278" s="1">
+        <v>0</v>
+      </c>
+      <c r="R278" s="1">
+        <v>3053.6333333333337</v>
+      </c>
     </row>
     <row r="279" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B279" s="4"/>
-      <c r="I279" s="1"/>
-      <c r="J279" s="1"/>
-      <c r="L279" s="1"/>
-      <c r="M279" s="1"/>
-      <c r="O279" s="1"/>
-      <c r="P279" s="1"/>
-      <c r="Q279" s="1"/>
-      <c r="R279" s="1"/>
+      <c r="A279" t="s">
+        <v>617</v>
+      </c>
+      <c r="B279" s="4">
+        <v>46324.608564814815</v>
+      </c>
+      <c r="C279" t="s">
+        <v>618</v>
+      </c>
+      <c r="D279" t="s">
+        <v>70</v>
+      </c>
+      <c r="E279" t="s">
+        <v>619</v>
+      </c>
+      <c r="F279" t="s">
+        <v>620</v>
+      </c>
+      <c r="G279" t="s">
+        <v>95</v>
+      </c>
+      <c r="H279">
+        <v>500</v>
+      </c>
+      <c r="I279" s="3">
+        <v>13.34</v>
+      </c>
+      <c r="J279" s="3">
+        <v>6670</v>
+      </c>
+      <c r="K279">
+        <v>0</v>
+      </c>
+      <c r="L279" s="3">
+        <v>0</v>
+      </c>
+      <c r="M279" s="3">
+        <v>0</v>
+      </c>
+      <c r="N279">
+        <v>0</v>
+      </c>
+      <c r="O279" s="3">
+        <v>0</v>
+      </c>
+      <c r="P279" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q279" s="1">
+        <v>0</v>
+      </c>
+      <c r="R279" s="1">
+        <v>6670</v>
+      </c>
     </row>
     <row r="280" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B280" s="4"/>
